--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126387774</v>
+        <v>126387767</v>
       </c>
       <c r="B3" t="n">
-        <v>91503</v>
+        <v>92724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697652</v>
+        <v>697567</v>
       </c>
       <c r="R3" t="n">
-        <v>7312419</v>
+        <v>7312415</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126387767</v>
+        <v>126387769</v>
       </c>
       <c r="B5" t="n">
         <v>92724</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697567</v>
+        <v>697652</v>
       </c>
       <c r="R5" t="n">
-        <v>7312415</v>
+        <v>7312419</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126387769</v>
+        <v>126387770</v>
       </c>
       <c r="B6" t="n">
-        <v>92724</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697652</v>
+        <v>697631</v>
       </c>
       <c r="R6" t="n">
-        <v>7312419</v>
+        <v>7312437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126387770</v>
+        <v>126387775</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697631</v>
+        <v>697546</v>
       </c>
       <c r="R7" t="n">
-        <v>7312437</v>
+        <v>7312408</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1239,6 +1239,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1257,10 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126387775</v>
+        <v>126387766</v>
       </c>
       <c r="B8" t="n">
-        <v>78644</v>
+        <v>75072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697546</v>
+        <v>697603</v>
       </c>
       <c r="R8" t="n">
-        <v>7312408</v>
+        <v>7312452</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,45 +1356,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126387766</v>
+        <v>126387763</v>
       </c>
       <c r="B9" t="n">
-        <v>75072</v>
+        <v>56848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697603</v>
+        <v>697614</v>
       </c>
       <c r="R9" t="n">
-        <v>7312452</v>
+        <v>7312438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1428,13 +1433,17 @@
           <t>2025-06-29</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1453,10 +1462,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126387763</v>
+        <v>126387765</v>
       </c>
       <c r="B10" t="n">
-        <v>56848</v>
+        <v>58025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1464,38 +1473,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697614</v>
+        <v>697472</v>
       </c>
       <c r="R10" t="n">
-        <v>7312438</v>
+        <v>7312435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,11 +1541,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1559,53 +1567,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126387765</v>
+        <v>126387772</v>
       </c>
       <c r="B11" t="n">
-        <v>58025</v>
+        <v>91403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697472</v>
+        <v>697650</v>
       </c>
       <c r="R11" t="n">
-        <v>7312435</v>
+        <v>7312428</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126387772</v>
+        <v>126387771</v>
       </c>
       <c r="B12" t="n">
-        <v>91403</v>
+        <v>79056</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697650</v>
+        <v>697390</v>
       </c>
       <c r="R12" t="n">
-        <v>7312428</v>
+        <v>7312543</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,45 +1761,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126387771</v>
+        <v>126387761</v>
       </c>
       <c r="B13" t="n">
-        <v>79056</v>
+        <v>56848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>697390</v>
+        <v>697572</v>
       </c>
       <c r="R13" t="n">
-        <v>7312543</v>
+        <v>7312418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1836,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126387761</v>
+        <v>126387776</v>
       </c>
       <c r="B14" t="n">
-        <v>56848</v>
+        <v>92532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1869,38 +1878,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697572</v>
+        <v>697723</v>
       </c>
       <c r="R14" t="n">
-        <v>7312418</v>
+        <v>7312440</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1933,11 +1938,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126387776</v>
+        <v>126429379</v>
       </c>
       <c r="B15" t="n">
-        <v>92532</v>
+        <v>92724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697723</v>
+        <v>697344</v>
       </c>
       <c r="R15" t="n">
-        <v>7312440</v>
+        <v>7312456</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2058,6 +2058,1394 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126387774</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91503</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>65</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>697650</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7312428</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126441134</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105372</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>697636</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7312436</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126441319</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>697393</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7312461</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126429376</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79566</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>697266</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7312481</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126440996</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97236</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>697636</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7312436</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126429382</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>697632</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7312442</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126429374</v>
+      </c>
+      <c r="B22" t="n">
+        <v>105372</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>697354</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7312456</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126429384</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78383</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>697375</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7312460</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126429375</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>697253</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7312498</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126429381</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>697306</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7312454</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126429383</v>
+      </c>
+      <c r="B26" t="n">
+        <v>77926</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>697242</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7312477</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126441004</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97233</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>697636</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7312436</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126429377</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91242</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>697256</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7312452</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126441387</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97236</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>697258</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7312485</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -2366,48 +2366,52 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126429376</v>
+        <v>126440996</v>
       </c>
       <c r="B19" t="n">
-        <v>79566</v>
+        <v>97236</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697266</v>
+        <v>697636</v>
       </c>
       <c r="R19" t="n">
-        <v>7312481</v>
+        <v>7312436</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2445,70 +2449,67 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126440996</v>
+        <v>126429376</v>
       </c>
       <c r="B20" t="n">
-        <v>97236</v>
+        <v>79566</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+          <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697636</v>
+        <v>697266</v>
       </c>
       <c r="R20" t="n">
-        <v>7312436</v>
+        <v>7312481</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2546,19 +2547,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126387773</v>
       </c>
       <c r="B2" t="n">
-        <v>91403</v>
+        <v>91406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126387767</v>
       </c>
       <c r="B3" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126387768</v>
       </c>
       <c r="B4" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126387769</v>
       </c>
       <c r="B5" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126387770</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126387775</v>
       </c>
       <c r="B7" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>126387766</v>
       </c>
       <c r="B8" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>126387763</v>
       </c>
       <c r="B9" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>126387765</v>
       </c>
       <c r="B10" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>126387772</v>
       </c>
       <c r="B11" t="n">
-        <v>91403</v>
+        <v>91406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>126387771</v>
       </c>
       <c r="B12" t="n">
-        <v>79056</v>
+        <v>79059</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>126387761</v>
       </c>
       <c r="B13" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>126387776</v>
       </c>
       <c r="B14" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>126429379</v>
       </c>
       <c r="B15" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>126387774</v>
       </c>
       <c r="B16" t="n">
-        <v>91503</v>
+        <v>91506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>126441134</v>
       </c>
       <c r="B17" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>126441319</v>
       </c>
       <c r="B18" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>126440996</v>
       </c>
       <c r="B19" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>126429376</v>
       </c>
       <c r="B20" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,32 +2565,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126429382</v>
+        <v>126429374</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>105381</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697632</v>
+        <v>697354</v>
       </c>
       <c r="R21" t="n">
-        <v>7312442</v>
+        <v>7312456</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,6 +2644,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2662,32 +2663,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126429374</v>
+        <v>126429382</v>
       </c>
       <c r="B22" t="n">
-        <v>105372</v>
+        <v>78980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2697,10 +2698,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697354</v>
+        <v>697632</v>
       </c>
       <c r="R22" t="n">
-        <v>7312456</v>
+        <v>7312442</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2742,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>126429384</v>
       </c>
       <c r="B23" t="n">
-        <v>78383</v>
+        <v>78386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>126429375</v>
       </c>
       <c r="B24" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>126429381</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>126429383</v>
       </c>
       <c r="B26" t="n">
-        <v>77926</v>
+        <v>77929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>126441004</v>
       </c>
       <c r="B27" t="n">
-        <v>97233</v>
+        <v>97242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>126429377</v>
       </c>
       <c r="B28" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>126441387</v>
       </c>
       <c r="B29" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -2366,52 +2366,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126440996</v>
+        <v>126429376</v>
       </c>
       <c r="B19" t="n">
-        <v>97245</v>
+        <v>79569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+          <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697636</v>
+        <v>697266</v>
       </c>
       <c r="R19" t="n">
-        <v>7312436</v>
+        <v>7312481</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2449,67 +2445,70 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126429376</v>
+        <v>126440996</v>
       </c>
       <c r="B20" t="n">
-        <v>79569</v>
+        <v>97245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697266</v>
+        <v>697636</v>
       </c>
       <c r="R20" t="n">
-        <v>7312481</v>
+        <v>7312436</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2547,18 +2546,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -3452,7 +3452,7 @@
         <v>126801482</v>
       </c>
       <c r="B30" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126801481</v>
       </c>
       <c r="B31" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>126801479</v>
       </c>
       <c r="B32" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>126801486</v>
       </c>
       <c r="B34" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>126801480</v>
       </c>
       <c r="B35" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -3452,7 +3452,7 @@
         <v>126801482</v>
       </c>
       <c r="B30" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126801481</v>
       </c>
       <c r="B31" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>126801479</v>
       </c>
       <c r="B32" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>126801486</v>
       </c>
       <c r="B34" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>126801480</v>
       </c>
       <c r="B35" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -3452,7 +3452,7 @@
         <v>126801482</v>
       </c>
       <c r="B30" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>126801479</v>
       </c>
       <c r="B32" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -3452,7 +3452,7 @@
         <v>126801482</v>
       </c>
       <c r="B30" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126801481</v>
       </c>
       <c r="B31" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>126801479</v>
       </c>
       <c r="B32" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>126801483</v>
       </c>
       <c r="B33" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>126801486</v>
       </c>
       <c r="B34" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>126801480</v>
       </c>
       <c r="B35" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>126801485</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>126801484</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4237,6 +4237,3777 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127671948</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79104</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>697440</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7312523</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127671947</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>697387</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7312552</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127671953</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97331</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>697260</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7312498</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127671935</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>697439</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7312528</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127671968</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>697330</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7312575</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127671941</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56853</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>697421</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7312530</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127671954</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78777</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>697348</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7312527</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127671939</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>697265</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7312540</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127671962</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>697316</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7312471</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127671957</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>697236</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7312490</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127671955</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>697329</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7312476</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127671958</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>697325</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7312452</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127671970</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>353</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>697381</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7312557</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>127671963</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>697302</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7312488</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>127675520</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79097</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>864</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>697413</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7312510</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127671964</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>697283</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7312520</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127675495</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>697413</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7312510</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127671932</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>697427</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7312533</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127671934</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>697440</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7312517</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127671928</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>185</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>697336</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7312539</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127671974</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>697240</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7312489</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127671929</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>697349</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7312528</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>127671952</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97325</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>697273</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7312509</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>127671960</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79097</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>864</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>697356</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7312567</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>127671936</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79607</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>697281</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7312520</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127671931</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>697282</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7312524</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127671961</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79097</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>864</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>697347</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7312562</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127671930</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79636</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>697297</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7312471</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127671969</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>697347</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7312584</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127671938</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>697414</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7312503</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127671959</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>697355</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7312481</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127675593</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>697356</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7312567</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>127671973</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91383</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>697309</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7312479</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127671945</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>697270</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7312519</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>127671965</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>697325</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7312536</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127671944</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57658</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>697355</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7312481</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127671972</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78424</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>697413</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7312510</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127671951</v>
+      </c>
+      <c r="B75" t="n">
+        <v>105471</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>697331</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7312443</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,45 +4239,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B38" t="n">
-        <v>79104</v>
+        <v>57658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R38" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4312,13 +4316,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4330,56 +4338,52 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671947</v>
+        <v>127671948</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>79104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697387</v>
+        <v>697440</v>
       </c>
       <c r="R39" t="n">
-        <v>7312552</v>
+        <v>7312523</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4414,17 +4418,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4734,45 +4734,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671941</v>
+        <v>127671939</v>
       </c>
       <c r="B43" t="n">
-        <v>56853</v>
+        <v>57661</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697421</v>
+        <v>697265</v>
       </c>
       <c r="R43" t="n">
-        <v>7312530</v>
+        <v>7312540</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,39 +4833,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671954</v>
+        <v>127671941</v>
       </c>
       <c r="B44" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4871,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697348</v>
+        <v>697421</v>
       </c>
       <c r="R44" t="n">
-        <v>7312527</v>
+        <v>7312530</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4909,13 +4913,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4934,10 +4942,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671939</v>
+        <v>127671954</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4945,38 +4953,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697265</v>
+        <v>697348</v>
       </c>
       <c r="R45" t="n">
-        <v>7312540</v>
+        <v>7312527</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5011,17 +5015,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5033,17 +5033,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671962</v>
+        <v>127671957</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,21 +5051,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>697316</v>
+        <v>697236</v>
       </c>
       <c r="R46" t="n">
-        <v>7312471</v>
+        <v>7312490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671957</v>
+        <v>127671962</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697236</v>
+        <v>697316</v>
       </c>
       <c r="R47" t="n">
-        <v>7312490</v>
+        <v>7312471</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5332,32 +5332,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671958</v>
+        <v>127671970</v>
       </c>
       <c r="B49" t="n">
-        <v>98448</v>
+        <v>78685</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697325</v>
+        <v>697381</v>
       </c>
       <c r="R49" t="n">
-        <v>7312452</v>
+        <v>7312557</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5403,11 +5403,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5435,10 +5430,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B50" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5446,21 +5441,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5470,10 +5465,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R50" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5514,7 +5509,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5526,14 +5520,14 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671963</v>
+        <v>127671964</v>
       </c>
       <c r="B51" t="n">
         <v>79018</v>
@@ -5568,10 +5562,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697302</v>
+        <v>697283</v>
       </c>
       <c r="R51" t="n">
-        <v>7312488</v>
+        <v>7312520</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5630,50 +5624,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127675520</v>
+        <v>127671958</v>
       </c>
       <c r="B52" t="n">
-        <v>79097</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697413</v>
+        <v>697325</v>
       </c>
       <c r="R52" t="n">
-        <v>7312510</v>
+        <v>7312452</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5708,6 +5697,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5726,17 +5720,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671964</v>
+        <v>127675520</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79097</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5744,34 +5738,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697283</v>
+        <v>697413</v>
       </c>
       <c r="R53" t="n">
-        <v>7312520</v>
+        <v>7312510</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5812,6 +5811,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127675495</v>
+        <v>127671928</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>79050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697413</v>
+        <v>697336</v>
       </c>
       <c r="R54" t="n">
-        <v>7312510</v>
+        <v>7312539</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127671934</v>
+        <v>127675495</v>
       </c>
       <c r="B56" t="n">
         <v>79636</v>
@@ -6057,16 +6057,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697440</v>
+        <v>697413</v>
       </c>
       <c r="R56" t="n">
-        <v>7312517</v>
+        <v>7312510</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6107,6 +6110,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6125,10 +6129,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671928</v>
+        <v>127671934</v>
       </c>
       <c r="B57" t="n">
-        <v>79050</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6136,37 +6140,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697336</v>
+        <v>697440</v>
       </c>
       <c r="R57" t="n">
-        <v>7312539</v>
+        <v>7312517</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6207,7 +6208,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,14 +6219,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127671974</v>
+        <v>127671929</v>
       </c>
       <c r="B58" t="n">
         <v>79636</v>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>697240</v>
+        <v>697349</v>
       </c>
       <c r="R58" t="n">
-        <v>7312489</v>
+        <v>7312528</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6323,7 +6323,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671929</v>
+        <v>127671974</v>
       </c>
       <c r="B59" t="n">
         <v>79636</v>
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>697349</v>
+        <v>697240</v>
       </c>
       <c r="R59" t="n">
-        <v>7312528</v>
+        <v>7312489</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7101,38 +7101,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127671938</v>
+        <v>127671959</v>
       </c>
       <c r="B67" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>697414</v>
+        <v>697355</v>
       </c>
       <c r="R67" t="n">
-        <v>7312503</v>
+        <v>7312481</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7189,6 +7189,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7207,38 +7208,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127671959</v>
+        <v>127671938</v>
       </c>
       <c r="B68" t="n">
-        <v>98448</v>
+        <v>57661</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7246,10 +7247,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697355</v>
+        <v>697414</v>
       </c>
       <c r="R68" t="n">
-        <v>7312481</v>
+        <v>7312503</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7286,7 +7287,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7295,7 +7296,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7314,48 +7314,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>91383</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R69" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7415,45 +7412,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B70" t="n">
-        <v>91383</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R70" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671945</v>
+        <v>127671972</v>
       </c>
       <c r="B71" t="n">
-        <v>57658</v>
+        <v>78424</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697270</v>
+        <v>697413</v>
       </c>
       <c r="R71" t="n">
-        <v>7312519</v>
+        <v>7312510</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,17 +7586,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7712,7 +7708,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671944</v>
+        <v>127671945</v>
       </c>
       <c r="B73" t="n">
         <v>57658</v>
@@ -7747,10 +7743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697355</v>
+        <v>697270</v>
       </c>
       <c r="R73" t="n">
-        <v>7312481</v>
+        <v>7312519</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7787,7 +7783,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>fodersök</t>
+          <t>fodersök och påbörjad bohål</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7814,10 +7810,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671972</v>
+        <v>127671944</v>
       </c>
       <c r="B74" t="n">
-        <v>78424</v>
+        <v>57658</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7825,21 +7821,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7849,10 +7845,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697413</v>
+        <v>697355</v>
       </c>
       <c r="R74" t="n">
-        <v>7312510</v>
+        <v>7312481</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7887,13 +7883,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8008,6 +8008,122 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127705223</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>697435</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7312514</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Heike Kontermann, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B49" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R49" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,7 +5411,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5423,14 +5422,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671963</v>
+        <v>127671964</v>
       </c>
       <c r="B50" t="n">
         <v>79018</v>
@@ -5465,10 +5464,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697302</v>
+        <v>697283</v>
       </c>
       <c r="R50" t="n">
-        <v>7312488</v>
+        <v>7312520</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5527,10 +5526,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671964</v>
+        <v>127675520</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79097</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5538,34 +5537,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697283</v>
+        <v>697413</v>
       </c>
       <c r="R51" t="n">
-        <v>7312520</v>
+        <v>7312510</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5606,6 +5610,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5624,32 +5629,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671958</v>
+        <v>127671970</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>78685</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5659,10 +5664,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697325</v>
+        <v>697381</v>
       </c>
       <c r="R52" t="n">
-        <v>7312452</v>
+        <v>7312557</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5695,11 +5700,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5727,50 +5727,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127675520</v>
+        <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>79097</v>
+        <v>98448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697413</v>
+        <v>697325</v>
       </c>
       <c r="R53" t="n">
-        <v>7312510</v>
+        <v>7312452</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5805,6 +5800,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B60" t="n">
-        <v>97325</v>
+        <v>79097</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R60" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,6 +6499,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6510,39 +6511,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B61" t="n">
-        <v>79097</v>
+        <v>97325</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6552,10 +6553,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R61" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6596,7 +6597,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671972</v>
+        <v>127671945</v>
       </c>
       <c r="B71" t="n">
-        <v>78424</v>
+        <v>57658</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697413</v>
+        <v>697270</v>
       </c>
       <c r="R71" t="n">
-        <v>7312510</v>
+        <v>7312519</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,13 +7586,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7615,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671965</v>
+        <v>127671944</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7622,21 +7626,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7646,10 +7650,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697325</v>
+        <v>697355</v>
       </c>
       <c r="R72" t="n">
-        <v>7312536</v>
+        <v>7312481</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7682,6 +7686,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7708,10 +7717,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671945</v>
+        <v>127671972</v>
       </c>
       <c r="B73" t="n">
-        <v>57658</v>
+        <v>78424</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7719,21 +7728,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7743,10 +7752,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697270</v>
+        <v>697413</v>
       </c>
       <c r="R73" t="n">
-        <v>7312519</v>
+        <v>7312510</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7781,17 +7790,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7810,10 +7815,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671944</v>
+        <v>127671965</v>
       </c>
       <c r="B74" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7821,21 +7826,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7845,10 +7850,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697355</v>
+        <v>697325</v>
       </c>
       <c r="R74" t="n">
-        <v>7312481</v>
+        <v>7312536</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7881,11 +7886,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,49 +4239,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671947</v>
+        <v>127671948</v>
       </c>
       <c r="B38" t="n">
-        <v>57658</v>
+        <v>79106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697387</v>
+        <v>697440</v>
       </c>
       <c r="R38" t="n">
-        <v>7312552</v>
+        <v>7312523</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4316,17 +4312,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4338,52 +4330,56 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B39" t="n">
-        <v>79104</v>
+        <v>57660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R39" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4418,13 +4414,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4446,7 +4446,7 @@
         <v>127671953</v>
       </c>
       <c r="B40" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127671935</v>
       </c>
       <c r="B41" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>127671968</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>127671939</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4840,32 +4840,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671941</v>
+        <v>127671954</v>
       </c>
       <c r="B44" t="n">
-        <v>56853</v>
+        <v>78779</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697421</v>
+        <v>697348</v>
       </c>
       <c r="R44" t="n">
-        <v>7312530</v>
+        <v>7312527</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,17 +4913,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4942,32 +4938,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671954</v>
+        <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>78777</v>
+        <v>56855</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4977,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697348</v>
+        <v>697421</v>
       </c>
       <c r="R45" t="n">
-        <v>7312527</v>
+        <v>7312530</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5015,13 +5011,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>127671957</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>127671962</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>127671955</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671963</v>
+        <v>127671970</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697302</v>
+        <v>697381</v>
       </c>
       <c r="R49" t="n">
-        <v>7312488</v>
+        <v>7312557</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,6 +5411,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5422,17 +5423,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671964</v>
+        <v>127675520</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79099</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5440,34 +5441,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697283</v>
+        <v>697413</v>
       </c>
       <c r="R50" t="n">
-        <v>7312520</v>
+        <v>7312510</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5508,6 +5514,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5526,10 +5533,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127675520</v>
+        <v>127671963</v>
       </c>
       <c r="B51" t="n">
-        <v>79097</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5537,39 +5544,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697413</v>
+        <v>697302</v>
       </c>
       <c r="R51" t="n">
-        <v>7312510</v>
+        <v>7312488</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5610,7 +5612,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5629,10 +5630,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671970</v>
+        <v>127671964</v>
       </c>
       <c r="B52" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5640,21 +5641,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5664,10 +5665,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697381</v>
+        <v>697283</v>
       </c>
       <c r="R52" t="n">
-        <v>7312557</v>
+        <v>7312520</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5708,7 +5709,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
         <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671928</v>
+        <v>127671934</v>
       </c>
       <c r="B54" t="n">
-        <v>79050</v>
+        <v>79638</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,37 +5841,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697336</v>
+        <v>697440</v>
       </c>
       <c r="R54" t="n">
-        <v>7312539</v>
+        <v>7312517</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5912,7 +5909,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5924,17 +5920,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671932</v>
+        <v>127671928</v>
       </c>
       <c r="B55" t="n">
-        <v>79636</v>
+        <v>79052</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5942,34 +5938,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697427</v>
+        <v>697336</v>
       </c>
       <c r="R55" t="n">
-        <v>7312533</v>
+        <v>7312539</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6010,6 +6009,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6021,17 +6021,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127675495</v>
+        <v>127671932</v>
       </c>
       <c r="B56" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6057,19 +6057,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697413</v>
+        <v>697427</v>
       </c>
       <c r="R56" t="n">
-        <v>7312510</v>
+        <v>7312533</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6110,7 +6107,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6129,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671934</v>
+        <v>127675495</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6158,16 +6154,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697440</v>
+        <v>697413</v>
       </c>
       <c r="R57" t="n">
-        <v>7312517</v>
+        <v>7312510</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6208,6 +6207,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>127671929</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>127671974</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>127671960</v>
       </c>
       <c r="B60" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>127671952</v>
       </c>
       <c r="B61" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,10 +6615,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B62" t="n">
-        <v>79607</v>
+        <v>79638</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R62" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B63" t="n">
-        <v>79636</v>
+        <v>79609</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R63" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127671961</v>
+        <v>127671930</v>
       </c>
       <c r="B64" t="n">
-        <v>79097</v>
+        <v>79638</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,21 +6820,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>697347</v>
+        <v>697297</v>
       </c>
       <c r="R64" t="n">
-        <v>7312562</v>
+        <v>7312471</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6888,7 +6888,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6900,17 +6899,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127671930</v>
+        <v>127671961</v>
       </c>
       <c r="B65" t="n">
-        <v>79636</v>
+        <v>79099</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6918,21 +6917,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6942,10 +6941,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>697297</v>
+        <v>697347</v>
       </c>
       <c r="R65" t="n">
-        <v>7312471</v>
+        <v>7312562</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6986,6 +6985,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7007,7 +7007,7 @@
         <v>127671969</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7101,38 +7101,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127671959</v>
+        <v>127671938</v>
       </c>
       <c r="B67" t="n">
-        <v>98448</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>697355</v>
+        <v>697414</v>
       </c>
       <c r="R67" t="n">
-        <v>7312481</v>
+        <v>7312503</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7189,7 +7189,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7208,38 +7207,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127671938</v>
+        <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>98450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7247,10 +7246,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697414</v>
+        <v>697355</v>
       </c>
       <c r="R68" t="n">
-        <v>7312503</v>
+        <v>7312481</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7287,7 +7286,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7296,6 +7295,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7314,45 +7314,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B69" t="n">
-        <v>91383</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R69" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7412,48 +7415,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>91385</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R70" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7516,7 +7516,7 @@
         <v>127671945</v>
       </c>
       <c r="B71" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>127671944</v>
       </c>
       <c r="B72" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>127671972</v>
       </c>
       <c r="B73" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>127671965</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>127671951</v>
       </c>
       <c r="B75" t="n">
-        <v>105471</v>
+        <v>105473</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>127705223</v>
       </c>
       <c r="B76" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671948</v>
+        <v>127671953</v>
       </c>
       <c r="B38" t="n">
-        <v>79106</v>
+        <v>97333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6450</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697440</v>
+        <v>697260</v>
       </c>
       <c r="R38" t="n">
-        <v>7312523</v>
+        <v>7312498</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4318,7 +4318,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4330,56 +4329,52 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671947</v>
+        <v>127671948</v>
       </c>
       <c r="B39" t="n">
-        <v>57660</v>
+        <v>79106</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697387</v>
+        <v>697440</v>
       </c>
       <c r="R39" t="n">
-        <v>7312552</v>
+        <v>7312523</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4414,17 +4409,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4436,52 +4427,56 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671953</v>
+        <v>127671947</v>
       </c>
       <c r="B40" t="n">
-        <v>97333</v>
+        <v>57660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697260</v>
+        <v>697387</v>
       </c>
       <c r="R40" t="n">
-        <v>7312498</v>
+        <v>7312552</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4514,6 +4509,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4734,49 +4734,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671939</v>
+        <v>127671941</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697265</v>
+        <v>697421</v>
       </c>
       <c r="R43" t="n">
-        <v>7312540</v>
+        <v>7312530</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4813,7 +4809,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4833,17 +4829,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671954</v>
+        <v>127671939</v>
       </c>
       <c r="B44" t="n">
-        <v>78779</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,34 +4847,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697348</v>
+        <v>697265</v>
       </c>
       <c r="R44" t="n">
-        <v>7312527</v>
+        <v>7312540</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,13 +4913,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4931,39 +4935,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671941</v>
+        <v>127671954</v>
       </c>
       <c r="B45" t="n">
-        <v>56855</v>
+        <v>78779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4977,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697421</v>
+        <v>697348</v>
       </c>
       <c r="R45" t="n">
-        <v>7312530</v>
+        <v>7312527</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5011,17 +5015,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B49" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R49" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,7 +5411,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5423,17 +5422,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127675520</v>
+        <v>127671964</v>
       </c>
       <c r="B50" t="n">
-        <v>79099</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5441,39 +5440,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697413</v>
+        <v>697283</v>
       </c>
       <c r="R50" t="n">
-        <v>7312510</v>
+        <v>7312520</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5514,7 +5508,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5533,10 +5526,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671963</v>
+        <v>127671970</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5544,21 +5537,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5568,10 +5561,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697302</v>
+        <v>697381</v>
       </c>
       <c r="R51" t="n">
-        <v>7312488</v>
+        <v>7312557</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5612,6 +5605,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5623,17 +5617,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671964</v>
+        <v>127675520</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>79099</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5641,34 +5635,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697283</v>
+        <v>697413</v>
       </c>
       <c r="R52" t="n">
-        <v>7312520</v>
+        <v>7312510</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5709,6 +5708,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671934</v>
+        <v>127671928</v>
       </c>
       <c r="B54" t="n">
-        <v>79638</v>
+        <v>79052</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,34 +5841,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697440</v>
+        <v>697336</v>
       </c>
       <c r="R54" t="n">
-        <v>7312517</v>
+        <v>7312539</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5909,6 +5912,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5920,17 +5924,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671928</v>
+        <v>127671932</v>
       </c>
       <c r="B55" t="n">
-        <v>79052</v>
+        <v>79638</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5938,37 +5942,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697336</v>
+        <v>697427</v>
       </c>
       <c r="R55" t="n">
-        <v>7312539</v>
+        <v>7312533</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6009,7 +6010,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6021,14 +6021,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127671932</v>
+        <v>127675495</v>
       </c>
       <c r="B56" t="n">
         <v>79638</v>
@@ -6057,16 +6057,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697427</v>
+        <v>697413</v>
       </c>
       <c r="R56" t="n">
-        <v>7312533</v>
+        <v>7312510</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6107,6 +6110,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6125,7 +6129,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127675495</v>
+        <v>127671934</v>
       </c>
       <c r="B57" t="n">
         <v>79638</v>
@@ -6154,19 +6158,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697413</v>
+        <v>697440</v>
       </c>
       <c r="R57" t="n">
-        <v>7312510</v>
+        <v>7312517</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6207,7 +6208,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7314,48 +7314,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>91385</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R69" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7415,45 +7412,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B70" t="n">
-        <v>91385</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R70" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671945</v>
+        <v>127671972</v>
       </c>
       <c r="B71" t="n">
-        <v>57660</v>
+        <v>78426</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697270</v>
+        <v>697413</v>
       </c>
       <c r="R71" t="n">
-        <v>7312519</v>
+        <v>7312510</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,17 +7586,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7615,10 +7611,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671944</v>
+        <v>127671965</v>
       </c>
       <c r="B72" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7626,21 +7622,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7650,10 +7646,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697355</v>
+        <v>697325</v>
       </c>
       <c r="R72" t="n">
-        <v>7312481</v>
+        <v>7312536</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7686,11 +7682,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7717,10 +7708,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671972</v>
+        <v>127671945</v>
       </c>
       <c r="B73" t="n">
-        <v>78426</v>
+        <v>57660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7728,21 +7719,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7752,10 +7743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697413</v>
+        <v>697270</v>
       </c>
       <c r="R73" t="n">
-        <v>7312510</v>
+        <v>7312519</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7790,13 +7781,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7815,10 +7810,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671965</v>
+        <v>127671944</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7826,21 +7821,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7850,10 +7845,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697325</v>
+        <v>697355</v>
       </c>
       <c r="R74" t="n">
-        <v>7312536</v>
+        <v>7312481</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7886,6 +7881,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -7101,38 +7101,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127671938</v>
+        <v>127671959</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>697414</v>
+        <v>697355</v>
       </c>
       <c r="R67" t="n">
-        <v>7312503</v>
+        <v>7312481</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7189,6 +7189,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7207,38 +7208,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127671959</v>
+        <v>127671938</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7246,10 +7247,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697355</v>
+        <v>697414</v>
       </c>
       <c r="R68" t="n">
-        <v>7312481</v>
+        <v>7312503</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7286,7 +7287,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7295,7 +7296,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,45 +4239,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671953</v>
+        <v>127671947</v>
       </c>
       <c r="B38" t="n">
-        <v>97333</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697260</v>
+        <v>697387</v>
       </c>
       <c r="R38" t="n">
-        <v>7312498</v>
+        <v>7312552</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4310,6 +4314,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4434,49 +4443,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671947</v>
+        <v>127671953</v>
       </c>
       <c r="B40" t="n">
-        <v>57660</v>
+        <v>97333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697387</v>
+        <v>697260</v>
       </c>
       <c r="R40" t="n">
-        <v>7312552</v>
+        <v>7312498</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4509,11 +4514,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4734,45 +4734,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671941</v>
+        <v>127671939</v>
       </c>
       <c r="B43" t="n">
-        <v>56855</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697421</v>
+        <v>697265</v>
       </c>
       <c r="R43" t="n">
-        <v>7312530</v>
+        <v>7312540</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,17 +4833,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671939</v>
+        <v>127671954</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>78779</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4847,38 +4851,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697265</v>
+        <v>697348</v>
       </c>
       <c r="R44" t="n">
-        <v>7312540</v>
+        <v>7312527</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,17 +4913,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4935,39 +4931,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671954</v>
+        <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>78779</v>
+        <v>56855</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4977,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697348</v>
+        <v>697421</v>
       </c>
       <c r="R45" t="n">
-        <v>7312527</v>
+        <v>7312530</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5015,13 +5011,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671962</v>
+        <v>127671955</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697316</v>
+        <v>697329</v>
       </c>
       <c r="R47" t="n">
-        <v>7312471</v>
+        <v>7312476</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5216,6 +5216,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5227,17 +5228,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127671955</v>
+        <v>127671962</v>
       </c>
       <c r="B48" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5245,21 +5246,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5269,10 +5270,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>697329</v>
+        <v>697316</v>
       </c>
       <c r="R48" t="n">
-        <v>7312476</v>
+        <v>7312471</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5313,7 +5314,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5526,32 +5526,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671970</v>
+        <v>127671958</v>
       </c>
       <c r="B51" t="n">
-        <v>78687</v>
+        <v>98450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697381</v>
+        <v>697325</v>
       </c>
       <c r="R51" t="n">
-        <v>7312557</v>
+        <v>7312452</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5597,6 +5597,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5727,32 +5732,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671958</v>
+        <v>127671970</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>78687</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5762,10 +5767,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697325</v>
+        <v>697381</v>
       </c>
       <c r="R53" t="n">
-        <v>7312452</v>
+        <v>7312557</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5798,11 +5803,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6809,10 +6809,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127671930</v>
+        <v>127671961</v>
       </c>
       <c r="B64" t="n">
-        <v>79638</v>
+        <v>79099</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,21 +6820,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>697297</v>
+        <v>697347</v>
       </c>
       <c r="R64" t="n">
-        <v>7312471</v>
+        <v>7312562</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6888,6 +6888,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6899,17 +6900,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127671961</v>
+        <v>127671930</v>
       </c>
       <c r="B65" t="n">
-        <v>79099</v>
+        <v>79638</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,21 +6918,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6941,10 +6942,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>697347</v>
+        <v>697297</v>
       </c>
       <c r="R65" t="n">
-        <v>7312562</v>
+        <v>7312471</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6985,7 +6986,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7101,38 +7101,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127671959</v>
+        <v>127671938</v>
       </c>
       <c r="B67" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>697355</v>
+        <v>697414</v>
       </c>
       <c r="R67" t="n">
-        <v>7312481</v>
+        <v>7312503</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7189,7 +7189,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7208,38 +7207,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127671938</v>
+        <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7247,10 +7246,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697414</v>
+        <v>697355</v>
       </c>
       <c r="R68" t="n">
-        <v>7312503</v>
+        <v>7312481</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7287,7 +7286,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7296,6 +7295,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7314,45 +7314,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B69" t="n">
-        <v>91385</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R69" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7412,48 +7415,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>91385</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R70" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671972</v>
+        <v>127671945</v>
       </c>
       <c r="B71" t="n">
-        <v>78426</v>
+        <v>57660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697413</v>
+        <v>697270</v>
       </c>
       <c r="R71" t="n">
-        <v>7312510</v>
+        <v>7312519</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,13 +7586,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7615,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671965</v>
+        <v>127671944</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7622,21 +7626,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7646,10 +7650,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697325</v>
+        <v>697355</v>
       </c>
       <c r="R72" t="n">
-        <v>7312536</v>
+        <v>7312481</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7682,6 +7686,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7708,10 +7717,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671945</v>
+        <v>127671972</v>
       </c>
       <c r="B73" t="n">
-        <v>57660</v>
+        <v>78426</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7719,21 +7728,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7743,10 +7752,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697270</v>
+        <v>697413</v>
       </c>
       <c r="R73" t="n">
-        <v>7312519</v>
+        <v>7312510</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7781,17 +7790,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7810,10 +7815,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671944</v>
+        <v>127671965</v>
       </c>
       <c r="B74" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7821,21 +7826,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7845,10 +7850,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697355</v>
+        <v>697325</v>
       </c>
       <c r="R74" t="n">
-        <v>7312481</v>
+        <v>7312536</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7881,11 +7886,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Steve Daurer, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,49 +4239,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671947</v>
+        <v>127671948</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>79106</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697387</v>
+        <v>697440</v>
       </c>
       <c r="R38" t="n">
-        <v>7312552</v>
+        <v>7312523</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4316,17 +4312,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4338,52 +4330,56 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B39" t="n">
-        <v>79106</v>
+        <v>57660</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R39" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4418,13 +4414,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4446,7 +4446,7 @@
         <v>127671953</v>
       </c>
       <c r="B40" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,49 +4734,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671939</v>
+        <v>127671941</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697265</v>
+        <v>697421</v>
       </c>
       <c r="R43" t="n">
-        <v>7312540</v>
+        <v>7312530</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4813,7 +4809,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4833,17 +4829,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671954</v>
+        <v>127671939</v>
       </c>
       <c r="B44" t="n">
-        <v>78779</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,34 +4847,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697348</v>
+        <v>697265</v>
       </c>
       <c r="R44" t="n">
-        <v>7312527</v>
+        <v>7312540</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,13 +4913,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4931,39 +4935,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671941</v>
+        <v>127671954</v>
       </c>
       <c r="B45" t="n">
-        <v>56855</v>
+        <v>78779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4977,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697421</v>
+        <v>697348</v>
       </c>
       <c r="R45" t="n">
-        <v>7312530</v>
+        <v>7312527</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5011,17 +5015,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671955</v>
+        <v>127671962</v>
       </c>
       <c r="B47" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697329</v>
+        <v>697316</v>
       </c>
       <c r="R47" t="n">
-        <v>7312476</v>
+        <v>7312471</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5216,7 +5216,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5228,17 +5227,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127671962</v>
+        <v>127671955</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5246,21 +5245,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5270,10 +5269,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>697316</v>
+        <v>697329</v>
       </c>
       <c r="R48" t="n">
-        <v>7312471</v>
+        <v>7312476</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5314,6 +5313,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5325,17 +5325,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671963</v>
+        <v>127671970</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697302</v>
+        <v>697381</v>
       </c>
       <c r="R49" t="n">
-        <v>7312488</v>
+        <v>7312557</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,6 +5411,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5422,17 +5423,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671964</v>
+        <v>127675520</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79099</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5440,34 +5441,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697283</v>
+        <v>697413</v>
       </c>
       <c r="R50" t="n">
-        <v>7312520</v>
+        <v>7312510</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5508,6 +5514,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5526,32 +5533,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671958</v>
+        <v>127671963</v>
       </c>
       <c r="B51" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5561,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697325</v>
+        <v>697302</v>
       </c>
       <c r="R51" t="n">
-        <v>7312452</v>
+        <v>7312488</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5599,18 +5606,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5622,17 +5623,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127675520</v>
+        <v>127671964</v>
       </c>
       <c r="B52" t="n">
-        <v>79099</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5640,39 +5641,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697413</v>
+        <v>697283</v>
       </c>
       <c r="R52" t="n">
-        <v>7312510</v>
+        <v>7312520</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5713,7 +5709,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5732,32 +5727,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671970</v>
+        <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>78687</v>
+        <v>98456</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,10 +5762,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697381</v>
+        <v>697325</v>
       </c>
       <c r="R53" t="n">
-        <v>7312557</v>
+        <v>7312452</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5803,6 +5798,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5830,10 +5830,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671928</v>
+        <v>127671932</v>
       </c>
       <c r="B54" t="n">
-        <v>79052</v>
+        <v>79638</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,37 +5841,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697336</v>
+        <v>697427</v>
       </c>
       <c r="R54" t="n">
-        <v>7312539</v>
+        <v>7312533</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5912,7 +5909,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5924,14 +5920,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671932</v>
+        <v>127675495</v>
       </c>
       <c r="B55" t="n">
         <v>79638</v>
@@ -5960,16 +5956,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697427</v>
+        <v>697413</v>
       </c>
       <c r="R55" t="n">
-        <v>7312533</v>
+        <v>7312510</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6010,6 +6009,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127675495</v>
+        <v>127671934</v>
       </c>
       <c r="B56" t="n">
         <v>79638</v>
@@ -6057,19 +6057,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697413</v>
+        <v>697440</v>
       </c>
       <c r="R56" t="n">
-        <v>7312510</v>
+        <v>7312517</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6110,7 +6107,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6129,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671934</v>
+        <v>127671928</v>
       </c>
       <c r="B57" t="n">
-        <v>79638</v>
+        <v>79052</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6140,34 +6136,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697440</v>
+        <v>697336</v>
       </c>
       <c r="R57" t="n">
-        <v>7312517</v>
+        <v>7312539</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6208,6 +6207,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6521,7 +6521,7 @@
         <v>127671952</v>
       </c>
       <c r="B61" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7314,48 +7314,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>91391</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R69" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7415,45 +7412,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B70" t="n">
-        <v>91385</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R70" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671945</v>
+        <v>127671972</v>
       </c>
       <c r="B71" t="n">
-        <v>57660</v>
+        <v>78426</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697270</v>
+        <v>697413</v>
       </c>
       <c r="R71" t="n">
-        <v>7312519</v>
+        <v>7312510</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,17 +7586,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7615,10 +7611,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671944</v>
+        <v>127671965</v>
       </c>
       <c r="B72" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7626,21 +7622,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7650,10 +7646,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697355</v>
+        <v>697325</v>
       </c>
       <c r="R72" t="n">
-        <v>7312481</v>
+        <v>7312536</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7686,11 +7682,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7717,10 +7708,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671972</v>
+        <v>127671945</v>
       </c>
       <c r="B73" t="n">
-        <v>78426</v>
+        <v>57660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7728,21 +7719,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7752,10 +7743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697413</v>
+        <v>697270</v>
       </c>
       <c r="R73" t="n">
-        <v>7312510</v>
+        <v>7312519</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7790,13 +7781,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7815,10 +7810,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671965</v>
+        <v>127671944</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7826,21 +7821,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7850,10 +7845,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697325</v>
+        <v>697355</v>
       </c>
       <c r="R74" t="n">
-        <v>7312536</v>
+        <v>7312481</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7886,6 +7881,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7915,7 +7915,7 @@
         <v>127671951</v>
       </c>
       <c r="B75" t="n">
-        <v>105473</v>
+        <v>105479</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Steve Daurer, Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4242,7 +4242,7 @@
         <v>127671948</v>
       </c>
       <c r="B38" t="n">
-        <v>79106</v>
+        <v>79109</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>127671947</v>
       </c>
       <c r="B39" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>127671953</v>
       </c>
       <c r="B40" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127671935</v>
       </c>
       <c r="B41" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>127671968</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4734,45 +4734,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671941</v>
+        <v>127671939</v>
       </c>
       <c r="B43" t="n">
-        <v>56855</v>
+        <v>57666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697421</v>
+        <v>697265</v>
       </c>
       <c r="R43" t="n">
-        <v>7312530</v>
+        <v>7312540</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,17 +4833,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671939</v>
+        <v>127671954</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>78782</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4847,38 +4851,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697265</v>
+        <v>697348</v>
       </c>
       <c r="R44" t="n">
-        <v>7312540</v>
+        <v>7312527</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,17 +4913,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4935,39 +4931,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671954</v>
+        <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>78779</v>
+        <v>56858</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4977,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697348</v>
+        <v>697421</v>
       </c>
       <c r="R45" t="n">
-        <v>7312527</v>
+        <v>7312530</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5015,13 +5011,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>127671957</v>
       </c>
       <c r="B46" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>127671962</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>127671955</v>
       </c>
       <c r="B48" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671970</v>
+        <v>127671964</v>
       </c>
       <c r="B49" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697381</v>
+        <v>697283</v>
       </c>
       <c r="R49" t="n">
-        <v>7312557</v>
+        <v>7312520</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,7 +5411,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5423,7 +5422,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5433,7 +5432,7 @@
         <v>127675520</v>
       </c>
       <c r="B50" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5533,10 +5532,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671963</v>
+        <v>127671970</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5544,21 +5543,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5568,10 +5567,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697302</v>
+        <v>697381</v>
       </c>
       <c r="R51" t="n">
-        <v>7312488</v>
+        <v>7312557</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5612,6 +5611,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671964</v>
+        <v>127671963</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697283</v>
+        <v>697302</v>
       </c>
       <c r="R52" t="n">
-        <v>7312520</v>
+        <v>7312488</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5730,7 +5730,7 @@
         <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671932</v>
+        <v>127675495</v>
       </c>
       <c r="B54" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5859,16 +5859,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697427</v>
+        <v>697413</v>
       </c>
       <c r="R54" t="n">
-        <v>7312533</v>
+        <v>7312510</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5909,6 +5912,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5927,10 +5931,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127675495</v>
+        <v>127671932</v>
       </c>
       <c r="B55" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5956,19 +5960,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697413</v>
+        <v>697427</v>
       </c>
       <c r="R55" t="n">
-        <v>7312510</v>
+        <v>7312533</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6009,7 +6010,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>127671934</v>
       </c>
       <c r="B56" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>127671928</v>
       </c>
       <c r="B57" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6226,10 +6226,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127671929</v>
+        <v>127671974</v>
       </c>
       <c r="B58" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>697349</v>
+        <v>697240</v>
       </c>
       <c r="R58" t="n">
-        <v>7312528</v>
+        <v>7312489</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671974</v>
+        <v>127671929</v>
       </c>
       <c r="B59" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>697240</v>
+        <v>697349</v>
       </c>
       <c r="R59" t="n">
-        <v>7312489</v>
+        <v>7312528</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B60" t="n">
-        <v>79099</v>
+        <v>97336</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R60" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,7 +6499,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6511,39 +6510,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B61" t="n">
-        <v>97333</v>
+        <v>79102</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6553,10 +6552,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R61" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6597,6 +6596,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,17 +6608,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B62" t="n">
-        <v>79638</v>
+        <v>79612</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R62" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B63" t="n">
-        <v>79609</v>
+        <v>79641</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R63" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6812,7 +6812,7 @@
         <v>127671961</v>
       </c>
       <c r="B64" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>127671930</v>
       </c>
       <c r="B65" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>127671969</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>127671938</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7314,45 +7314,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B69" t="n">
-        <v>91391</v>
+        <v>79023</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R69" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7412,48 +7415,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>91394</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R70" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671972</v>
+        <v>127671965</v>
       </c>
       <c r="B71" t="n">
-        <v>78426</v>
+        <v>79023</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697413</v>
+        <v>697325</v>
       </c>
       <c r="R71" t="n">
-        <v>7312510</v>
+        <v>7312536</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7592,7 +7592,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7610,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671965</v>
+        <v>127671972</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>78429</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7622,21 +7621,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7646,10 +7645,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697325</v>
+        <v>697413</v>
       </c>
       <c r="R72" t="n">
-        <v>7312536</v>
+        <v>7312510</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7690,6 +7689,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>127671945</v>
       </c>
       <c r="B73" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>127671944</v>
       </c>
       <c r="B74" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>127671951</v>
       </c>
       <c r="B75" t="n">
-        <v>105479</v>
+        <v>105482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>127705223</v>
       </c>
       <c r="B76" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4242,7 +4242,7 @@
         <v>127671948</v>
       </c>
       <c r="B38" t="n">
-        <v>79109</v>
+        <v>79115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>127671947</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>127671953</v>
       </c>
       <c r="B40" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>127671935</v>
       </c>
       <c r="B41" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>127671968</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>127671939</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4840,32 +4840,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671954</v>
+        <v>127671941</v>
       </c>
       <c r="B44" t="n">
-        <v>78782</v>
+        <v>56864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697348</v>
+        <v>697421</v>
       </c>
       <c r="R44" t="n">
-        <v>7312527</v>
+        <v>7312530</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,13 +4913,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4938,32 +4942,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671941</v>
+        <v>127671954</v>
       </c>
       <c r="B45" t="n">
-        <v>56858</v>
+        <v>78788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4977,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697421</v>
+        <v>697348</v>
       </c>
       <c r="R45" t="n">
-        <v>7312530</v>
+        <v>7312527</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5011,17 +5015,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>127671957</v>
       </c>
       <c r="B46" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>127671962</v>
       </c>
       <c r="B47" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>127671955</v>
       </c>
       <c r="B48" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671964</v>
+        <v>127671970</v>
       </c>
       <c r="B49" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697283</v>
+        <v>697381</v>
       </c>
       <c r="R49" t="n">
-        <v>7312520</v>
+        <v>7312557</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,6 +5411,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5422,7 +5423,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5432,7 +5433,7 @@
         <v>127675520</v>
       </c>
       <c r="B50" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5532,10 +5533,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B51" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5543,21 +5544,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5567,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R51" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5611,7 +5612,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671963</v>
+        <v>127671964</v>
       </c>
       <c r="B52" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697302</v>
+        <v>697283</v>
       </c>
       <c r="R52" t="n">
-        <v>7312488</v>
+        <v>7312520</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5730,7 +5730,7 @@
         <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127675495</v>
+        <v>127671928</v>
       </c>
       <c r="B54" t="n">
-        <v>79641</v>
+        <v>79061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697413</v>
+        <v>697336</v>
       </c>
       <c r="R54" t="n">
-        <v>7312510</v>
+        <v>7312539</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5934,7 +5934,7 @@
         <v>127671932</v>
       </c>
       <c r="B55" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127671934</v>
+        <v>127675495</v>
       </c>
       <c r="B56" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6057,16 +6057,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697440</v>
+        <v>697413</v>
       </c>
       <c r="R56" t="n">
-        <v>7312517</v>
+        <v>7312510</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6107,6 +6110,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6125,10 +6129,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671928</v>
+        <v>127671934</v>
       </c>
       <c r="B57" t="n">
-        <v>79055</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6136,37 +6140,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697336</v>
+        <v>697440</v>
       </c>
       <c r="R57" t="n">
-        <v>7312539</v>
+        <v>7312517</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6207,7 +6208,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127671974</v>
+        <v>127671929</v>
       </c>
       <c r="B58" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>697240</v>
+        <v>697349</v>
       </c>
       <c r="R58" t="n">
-        <v>7312489</v>
+        <v>7312528</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671929</v>
+        <v>127671974</v>
       </c>
       <c r="B59" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>697349</v>
+        <v>697240</v>
       </c>
       <c r="R59" t="n">
-        <v>7312528</v>
+        <v>7312489</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B60" t="n">
-        <v>97336</v>
+        <v>79108</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R60" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,6 +6499,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6510,39 +6511,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B61" t="n">
-        <v>79102</v>
+        <v>97344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6552,10 +6553,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R61" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6596,7 +6597,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,17 +6608,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B62" t="n">
-        <v>79612</v>
+        <v>79647</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R62" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B63" t="n">
-        <v>79641</v>
+        <v>79618</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R63" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6812,7 +6812,7 @@
         <v>127671961</v>
       </c>
       <c r="B64" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>127671930</v>
       </c>
       <c r="B65" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>127671969</v>
       </c>
       <c r="B66" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>127671938</v>
       </c>
       <c r="B67" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>127675593</v>
       </c>
       <c r="B69" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>127671973</v>
       </c>
       <c r="B70" t="n">
-        <v>91394</v>
+        <v>91402</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671965</v>
+        <v>127671972</v>
       </c>
       <c r="B71" t="n">
-        <v>79023</v>
+        <v>78435</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697325</v>
+        <v>697413</v>
       </c>
       <c r="R71" t="n">
-        <v>7312536</v>
+        <v>7312510</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7592,6 +7592,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7610,10 +7611,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671972</v>
+        <v>127671965</v>
       </c>
       <c r="B72" t="n">
-        <v>78429</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7621,21 +7622,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7645,10 +7646,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697413</v>
+        <v>697325</v>
       </c>
       <c r="R72" t="n">
-        <v>7312510</v>
+        <v>7312536</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7689,7 +7690,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7708,10 +7708,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671945</v>
+        <v>127671944</v>
       </c>
       <c r="B73" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697270</v>
+        <v>697355</v>
       </c>
       <c r="R73" t="n">
-        <v>7312519</v>
+        <v>7312481</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>fodersök och påbörjad bohål</t>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7810,10 +7810,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671944</v>
+        <v>127671945</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7845,10 +7845,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697355</v>
+        <v>697270</v>
       </c>
       <c r="R74" t="n">
-        <v>7312481</v>
+        <v>7312519</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>fodersök</t>
+          <t>fodersök och påbörjad bohål</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7915,7 +7915,7 @@
         <v>127671951</v>
       </c>
       <c r="B75" t="n">
-        <v>105482</v>
+        <v>105490</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>127705223</v>
       </c>
       <c r="B76" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,45 +4239,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>57669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R38" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4312,13 +4316,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4330,56 +4338,52 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671947</v>
+        <v>127671953</v>
       </c>
       <c r="B39" t="n">
-        <v>57669</v>
+        <v>97351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697387</v>
+        <v>697260</v>
       </c>
       <c r="R39" t="n">
-        <v>7312552</v>
+        <v>7312498</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4412,11 +4416,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4443,10 +4442,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671953</v>
+        <v>127671948</v>
       </c>
       <c r="B40" t="n">
-        <v>97350</v>
+        <v>79115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4454,21 +4453,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>6450</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4478,10 +4477,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697260</v>
+        <v>697440</v>
       </c>
       <c r="R40" t="n">
-        <v>7312498</v>
+        <v>7312523</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4522,6 +4521,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671957</v>
+        <v>127671962</v>
       </c>
       <c r="B46" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,21 +5051,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>697236</v>
+        <v>697316</v>
       </c>
       <c r="R46" t="n">
-        <v>7312490</v>
+        <v>7312471</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671962</v>
+        <v>127671957</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697316</v>
+        <v>697236</v>
       </c>
       <c r="R47" t="n">
-        <v>7312471</v>
+        <v>7312490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B49" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R49" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,7 +5411,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5423,17 +5422,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127675520</v>
+        <v>127671964</v>
       </c>
       <c r="B50" t="n">
-        <v>79108</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5441,39 +5440,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697413</v>
+        <v>697283</v>
       </c>
       <c r="R50" t="n">
-        <v>7312510</v>
+        <v>7312520</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5514,7 +5508,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5533,10 +5526,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671963</v>
+        <v>127675520</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79108</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5544,34 +5537,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697302</v>
+        <v>697413</v>
       </c>
       <c r="R51" t="n">
-        <v>7312488</v>
+        <v>7312510</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5612,6 +5610,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5630,10 +5629,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671964</v>
+        <v>127671970</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5641,21 +5640,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5665,10 +5664,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697283</v>
+        <v>697381</v>
       </c>
       <c r="R52" t="n">
-        <v>7312520</v>
+        <v>7312557</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5709,6 +5708,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5730,7 +5730,7 @@
         <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>127671952</v>
       </c>
       <c r="B61" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>127671973</v>
       </c>
       <c r="B70" t="n">
-        <v>91402</v>
+        <v>91403</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671944</v>
+        <v>127671945</v>
       </c>
       <c r="B73" t="n">
         <v>57669</v>
@@ -7743,10 +7743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697355</v>
+        <v>697270</v>
       </c>
       <c r="R73" t="n">
-        <v>7312481</v>
+        <v>7312519</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>fodersök</t>
+          <t>fodersök och påbörjad bohål</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7810,7 +7810,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671945</v>
+        <v>127671944</v>
       </c>
       <c r="B74" t="n">
         <v>57669</v>
@@ -7845,10 +7845,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697270</v>
+        <v>697355</v>
       </c>
       <c r="R74" t="n">
-        <v>7312519</v>
+        <v>7312481</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>fodersök och påbörjad bohål</t>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7915,7 +7915,7 @@
         <v>127671951</v>
       </c>
       <c r="B75" t="n">
-        <v>105490</v>
+        <v>105491</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,49 +4239,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671947</v>
+        <v>127671953</v>
       </c>
       <c r="B38" t="n">
-        <v>57669</v>
+        <v>97351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697387</v>
+        <v>697260</v>
       </c>
       <c r="R38" t="n">
-        <v>7312552</v>
+        <v>7312498</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4314,11 +4310,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4345,10 +4336,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671953</v>
+        <v>127671948</v>
       </c>
       <c r="B39" t="n">
-        <v>97351</v>
+        <v>79115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4356,21 +4347,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>6450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4380,10 +4371,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697260</v>
+        <v>697440</v>
       </c>
       <c r="R39" t="n">
-        <v>7312498</v>
+        <v>7312523</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4424,6 +4415,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4435,52 +4427,56 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B40" t="n">
-        <v>79115</v>
+        <v>57669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R40" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4515,13 +4511,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4734,49 +4734,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671939</v>
+        <v>127671941</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697265</v>
+        <v>697421</v>
       </c>
       <c r="R43" t="n">
-        <v>7312540</v>
+        <v>7312530</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4813,7 +4809,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4833,39 +4829,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671941</v>
+        <v>127671954</v>
       </c>
       <c r="B44" t="n">
-        <v>56864</v>
+        <v>78788</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4871,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697421</v>
+        <v>697348</v>
       </c>
       <c r="R44" t="n">
-        <v>7312530</v>
+        <v>7312527</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,17 +4909,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4942,10 +4934,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671954</v>
+        <v>127671939</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4953,34 +4945,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697348</v>
+        <v>697265</v>
       </c>
       <c r="R45" t="n">
-        <v>7312527</v>
+        <v>7312540</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5015,13 +5011,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5033,17 +5033,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671962</v>
+        <v>127671957</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,21 +5051,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>697316</v>
+        <v>697236</v>
       </c>
       <c r="R46" t="n">
-        <v>7312471</v>
+        <v>7312490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671957</v>
+        <v>127671962</v>
       </c>
       <c r="B47" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697236</v>
+        <v>697316</v>
       </c>
       <c r="R47" t="n">
-        <v>7312490</v>
+        <v>7312471</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671963</v>
+        <v>127675520</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,34 +5343,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697302</v>
+        <v>697413</v>
       </c>
       <c r="R49" t="n">
-        <v>7312488</v>
+        <v>7312510</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,6 +5416,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5429,10 +5435,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671964</v>
+        <v>127671970</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5440,21 +5446,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5464,10 +5470,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697283</v>
+        <v>697381</v>
       </c>
       <c r="R50" t="n">
-        <v>7312520</v>
+        <v>7312557</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5508,6 +5514,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5519,17 +5526,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127675520</v>
+        <v>127671963</v>
       </c>
       <c r="B51" t="n">
-        <v>79108</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5537,39 +5544,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697413</v>
+        <v>697302</v>
       </c>
       <c r="R51" t="n">
-        <v>7312510</v>
+        <v>7312488</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5610,7 +5612,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5629,10 +5630,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671970</v>
+        <v>127671964</v>
       </c>
       <c r="B52" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5640,21 +5641,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5664,10 +5665,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697381</v>
+        <v>697283</v>
       </c>
       <c r="R52" t="n">
-        <v>7312557</v>
+        <v>7312520</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5708,7 +5709,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B60" t="n">
-        <v>79108</v>
+        <v>97345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R60" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,7 +6499,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6511,39 +6510,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B61" t="n">
-        <v>97345</v>
+        <v>79108</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6553,10 +6552,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R61" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6597,6 +6596,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7314,48 +7314,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>91403</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R69" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7415,45 +7412,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B70" t="n">
-        <v>91403</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R70" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671972</v>
+        <v>127671945</v>
       </c>
       <c r="B71" t="n">
-        <v>78435</v>
+        <v>57669</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697413</v>
+        <v>697270</v>
       </c>
       <c r="R71" t="n">
-        <v>7312510</v>
+        <v>7312519</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,13 +7586,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7615,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671965</v>
+        <v>127671944</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7622,21 +7626,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7646,10 +7650,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697325</v>
+        <v>697355</v>
       </c>
       <c r="R72" t="n">
-        <v>7312536</v>
+        <v>7312481</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7682,6 +7686,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7708,10 +7717,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671945</v>
+        <v>127671972</v>
       </c>
       <c r="B73" t="n">
-        <v>57669</v>
+        <v>78435</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7719,21 +7728,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7743,10 +7752,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697270</v>
+        <v>697413</v>
       </c>
       <c r="R73" t="n">
-        <v>7312519</v>
+        <v>7312510</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7781,17 +7790,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7810,10 +7815,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671944</v>
+        <v>127671965</v>
       </c>
       <c r="B74" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7821,21 +7826,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7845,10 +7850,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697355</v>
+        <v>697325</v>
       </c>
       <c r="R74" t="n">
-        <v>7312481</v>
+        <v>7312536</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7881,11 +7886,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,10 +4239,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671953</v>
+        <v>127671948</v>
       </c>
       <c r="B38" t="n">
-        <v>97351</v>
+        <v>79115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>6450</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697260</v>
+        <v>697440</v>
       </c>
       <c r="R38" t="n">
-        <v>7312498</v>
+        <v>7312523</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4318,6 +4318,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4329,52 +4330,56 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B39" t="n">
-        <v>79115</v>
+        <v>57669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R39" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4409,13 +4414,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4427,56 +4436,52 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671947</v>
+        <v>127671953</v>
       </c>
       <c r="B40" t="n">
-        <v>57669</v>
+        <v>97352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697387</v>
+        <v>697260</v>
       </c>
       <c r="R40" t="n">
-        <v>7312552</v>
+        <v>7312498</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4509,11 +4514,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4734,45 +4734,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671941</v>
+        <v>127671939</v>
       </c>
       <c r="B43" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697421</v>
+        <v>697265</v>
       </c>
       <c r="R43" t="n">
-        <v>7312530</v>
+        <v>7312540</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4829,39 +4833,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671954</v>
+        <v>127671941</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>56864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4871,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697348</v>
+        <v>697421</v>
       </c>
       <c r="R44" t="n">
-        <v>7312527</v>
+        <v>7312530</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4909,13 +4913,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4934,10 +4942,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671939</v>
+        <v>127671954</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4945,38 +4953,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697265</v>
+        <v>697348</v>
       </c>
       <c r="R45" t="n">
-        <v>7312540</v>
+        <v>7312527</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5011,17 +5015,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5533,32 +5533,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671963</v>
+        <v>127671958</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697302</v>
+        <v>697325</v>
       </c>
       <c r="R51" t="n">
-        <v>7312488</v>
+        <v>7312452</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5606,12 +5606,18 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5623,14 +5629,14 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671964</v>
+        <v>127671963</v>
       </c>
       <c r="B52" t="n">
         <v>79029</v>
@@ -5665,10 +5671,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697283</v>
+        <v>697302</v>
       </c>
       <c r="R52" t="n">
-        <v>7312520</v>
+        <v>7312488</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5727,32 +5733,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671958</v>
+        <v>127671964</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5762,10 +5768,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697325</v>
+        <v>697283</v>
       </c>
       <c r="R53" t="n">
-        <v>7312452</v>
+        <v>7312520</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5800,18 +5806,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671928</v>
+        <v>127671932</v>
       </c>
       <c r="B54" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,37 +5841,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697336</v>
+        <v>697427</v>
       </c>
       <c r="R54" t="n">
-        <v>7312539</v>
+        <v>7312533</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5912,7 +5909,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5924,14 +5920,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671932</v>
+        <v>127675495</v>
       </c>
       <c r="B55" t="n">
         <v>79647</v>
@@ -5960,16 +5956,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697427</v>
+        <v>697413</v>
       </c>
       <c r="R55" t="n">
-        <v>7312533</v>
+        <v>7312510</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6010,6 +6009,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127675495</v>
+        <v>127671934</v>
       </c>
       <c r="B56" t="n">
         <v>79647</v>
@@ -6057,19 +6057,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697413</v>
+        <v>697440</v>
       </c>
       <c r="R56" t="n">
-        <v>7312510</v>
+        <v>7312517</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6110,7 +6107,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6129,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671934</v>
+        <v>127671928</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6140,34 +6136,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697440</v>
+        <v>697336</v>
       </c>
       <c r="R57" t="n">
-        <v>7312517</v>
+        <v>7312539</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6208,6 +6207,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6423,7 +6423,7 @@
         <v>127671952</v>
       </c>
       <c r="B60" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7314,45 +7314,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B69" t="n">
-        <v>91403</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R69" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7412,48 +7415,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>91404</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R70" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671945</v>
+        <v>127671972</v>
       </c>
       <c r="B71" t="n">
-        <v>57669</v>
+        <v>78435</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697270</v>
+        <v>697413</v>
       </c>
       <c r="R71" t="n">
-        <v>7312519</v>
+        <v>7312510</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,17 +7586,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7615,10 +7611,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671944</v>
+        <v>127671965</v>
       </c>
       <c r="B72" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7626,21 +7622,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7650,10 +7646,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697355</v>
+        <v>697325</v>
       </c>
       <c r="R72" t="n">
-        <v>7312481</v>
+        <v>7312536</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7686,11 +7682,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7717,10 +7708,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671972</v>
+        <v>127671944</v>
       </c>
       <c r="B73" t="n">
-        <v>78435</v>
+        <v>57669</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7728,21 +7719,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7752,10 +7743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697413</v>
+        <v>697355</v>
       </c>
       <c r="R73" t="n">
-        <v>7312510</v>
+        <v>7312481</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7790,13 +7781,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7815,10 +7810,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671965</v>
+        <v>127671945</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7826,21 +7821,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7850,10 +7845,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697325</v>
+        <v>697270</v>
       </c>
       <c r="R74" t="n">
-        <v>7312536</v>
+        <v>7312519</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7886,6 +7881,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7915,7 +7915,7 @@
         <v>127671951</v>
       </c>
       <c r="B75" t="n">
-        <v>105491</v>
+        <v>105492</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4446,7 +4446,7 @@
         <v>127671953</v>
       </c>
       <c r="B40" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4734,49 +4734,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671939</v>
+        <v>127671941</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>56864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697265</v>
+        <v>697421</v>
       </c>
       <c r="R43" t="n">
-        <v>7312540</v>
+        <v>7312530</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4813,7 +4809,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4833,52 +4829,56 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671941</v>
+        <v>127671939</v>
       </c>
       <c r="B44" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697421</v>
+        <v>697265</v>
       </c>
       <c r="R44" t="n">
-        <v>7312530</v>
+        <v>7312540</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>spillning</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671957</v>
+        <v>127671962</v>
       </c>
       <c r="B46" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,21 +5051,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>697236</v>
+        <v>697316</v>
       </c>
       <c r="R46" t="n">
-        <v>7312490</v>
+        <v>7312471</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671962</v>
+        <v>127671957</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697316</v>
+        <v>697236</v>
       </c>
       <c r="R47" t="n">
-        <v>7312471</v>
+        <v>7312490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127675520</v>
+        <v>127671964</v>
       </c>
       <c r="B49" t="n">
-        <v>79108</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,39 +5343,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697413</v>
+        <v>697283</v>
       </c>
       <c r="R49" t="n">
-        <v>7312510</v>
+        <v>7312520</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5416,7 +5411,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5435,10 +5429,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B50" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5446,21 +5440,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5470,10 +5464,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R50" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5514,7 +5508,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5526,52 +5519,57 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671958</v>
+        <v>127675520</v>
       </c>
       <c r="B51" t="n">
-        <v>98469</v>
+        <v>79108</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697325</v>
+        <v>697413</v>
       </c>
       <c r="R51" t="n">
-        <v>7312452</v>
+        <v>7312510</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5606,11 +5604,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5629,17 +5622,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671963</v>
+        <v>127671970</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5647,21 +5640,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5671,10 +5664,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697302</v>
+        <v>697381</v>
       </c>
       <c r="R52" t="n">
-        <v>7312488</v>
+        <v>7312557</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5715,6 +5708,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5726,39 +5720,39 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671964</v>
+        <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,10 +5762,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697283</v>
+        <v>697325</v>
       </c>
       <c r="R53" t="n">
-        <v>7312520</v>
+        <v>7312452</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5806,12 +5800,18 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671932</v>
+        <v>127671928</v>
       </c>
       <c r="B54" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,34 +5841,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697427</v>
+        <v>697336</v>
       </c>
       <c r="R54" t="n">
-        <v>7312533</v>
+        <v>7312539</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5909,6 +5912,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5920,14 +5924,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127675495</v>
+        <v>127671932</v>
       </c>
       <c r="B55" t="n">
         <v>79647</v>
@@ -5956,19 +5960,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697413</v>
+        <v>697427</v>
       </c>
       <c r="R55" t="n">
-        <v>7312510</v>
+        <v>7312533</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6009,7 +6010,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127671934</v>
+        <v>127675495</v>
       </c>
       <c r="B56" t="n">
         <v>79647</v>
@@ -6057,16 +6057,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697440</v>
+        <v>697413</v>
       </c>
       <c r="R56" t="n">
-        <v>7312517</v>
+        <v>7312510</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6107,6 +6110,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6125,10 +6129,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671928</v>
+        <v>127671934</v>
       </c>
       <c r="B57" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6136,37 +6140,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697336</v>
+        <v>697440</v>
       </c>
       <c r="R57" t="n">
-        <v>7312539</v>
+        <v>7312517</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6207,7 +6208,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B60" t="n">
-        <v>97346</v>
+        <v>79108</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R60" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,6 +6499,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6510,39 +6511,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B61" t="n">
-        <v>79108</v>
+        <v>97347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6552,10 +6553,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R61" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6596,7 +6597,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,17 +6608,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B62" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R62" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B63" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R63" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127671961</v>
+        <v>127671930</v>
       </c>
       <c r="B64" t="n">
-        <v>79108</v>
+        <v>79647</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,21 +6820,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>697347</v>
+        <v>697297</v>
       </c>
       <c r="R64" t="n">
-        <v>7312562</v>
+        <v>7312471</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6888,7 +6888,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6900,17 +6899,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127671930</v>
+        <v>127671961</v>
       </c>
       <c r="B65" t="n">
-        <v>79647</v>
+        <v>79108</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6918,21 +6917,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6942,10 +6941,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>697297</v>
+        <v>697347</v>
       </c>
       <c r="R65" t="n">
-        <v>7312471</v>
+        <v>7312562</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6986,6 +6985,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7210,7 +7210,7 @@
         <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>127671973</v>
       </c>
       <c r="B70" t="n">
-        <v>91404</v>
+        <v>91405</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671972</v>
+        <v>127671945</v>
       </c>
       <c r="B71" t="n">
-        <v>78435</v>
+        <v>57669</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697413</v>
+        <v>697270</v>
       </c>
       <c r="R71" t="n">
-        <v>7312510</v>
+        <v>7312519</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,13 +7586,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7615,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671965</v>
+        <v>127671944</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7622,21 +7626,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7646,10 +7650,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697325</v>
+        <v>697355</v>
       </c>
       <c r="R72" t="n">
-        <v>7312536</v>
+        <v>7312481</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7682,6 +7686,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7708,10 +7717,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671944</v>
+        <v>127671972</v>
       </c>
       <c r="B73" t="n">
-        <v>57669</v>
+        <v>78435</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7719,21 +7728,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7743,10 +7752,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697355</v>
+        <v>697413</v>
       </c>
       <c r="R73" t="n">
-        <v>7312481</v>
+        <v>7312510</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7781,17 +7790,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7810,10 +7815,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671945</v>
+        <v>127671965</v>
       </c>
       <c r="B74" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7821,21 +7826,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7845,10 +7850,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697270</v>
+        <v>697325</v>
       </c>
       <c r="R74" t="n">
-        <v>7312519</v>
+        <v>7312536</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7881,11 +7886,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7915,7 +7915,7 @@
         <v>127671951</v>
       </c>
       <c r="B75" t="n">
-        <v>105492</v>
+        <v>105493</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,45 +4239,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>57669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R38" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4312,13 +4316,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4330,56 +4338,52 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671947</v>
+        <v>127671948</v>
       </c>
       <c r="B39" t="n">
-        <v>57669</v>
+        <v>79115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697387</v>
+        <v>697440</v>
       </c>
       <c r="R39" t="n">
-        <v>7312552</v>
+        <v>7312523</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4414,17 +4418,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671962</v>
+        <v>127671957</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,21 +5051,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>697316</v>
+        <v>697236</v>
       </c>
       <c r="R46" t="n">
-        <v>7312471</v>
+        <v>7312490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671957</v>
+        <v>127671962</v>
       </c>
       <c r="B47" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697236</v>
+        <v>697316</v>
       </c>
       <c r="R47" t="n">
-        <v>7312490</v>
+        <v>7312471</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671964</v>
+        <v>127671970</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697283</v>
+        <v>697381</v>
       </c>
       <c r="R49" t="n">
-        <v>7312520</v>
+        <v>7312557</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,6 +5411,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5422,39 +5423,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671963</v>
+        <v>127671958</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5464,10 +5465,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697302</v>
+        <v>697325</v>
       </c>
       <c r="R50" t="n">
-        <v>7312488</v>
+        <v>7312452</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5502,12 +5503,18 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5519,7 +5526,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5629,10 +5636,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B52" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5640,21 +5647,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5664,10 +5671,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R52" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5708,7 +5715,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5720,39 +5726,39 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671958</v>
+        <v>127671964</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5762,10 +5768,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697325</v>
+        <v>697283</v>
       </c>
       <c r="R53" t="n">
-        <v>7312452</v>
+        <v>7312520</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5800,18 +5806,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671928</v>
+        <v>127671932</v>
       </c>
       <c r="B54" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,37 +5841,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697336</v>
+        <v>697427</v>
       </c>
       <c r="R54" t="n">
-        <v>7312539</v>
+        <v>7312533</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5912,7 +5909,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5924,14 +5920,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671932</v>
+        <v>127675495</v>
       </c>
       <c r="B55" t="n">
         <v>79647</v>
@@ -5960,16 +5956,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697427</v>
+        <v>697413</v>
       </c>
       <c r="R55" t="n">
-        <v>7312533</v>
+        <v>7312510</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6010,6 +6009,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127675495</v>
+        <v>127671934</v>
       </c>
       <c r="B56" t="n">
         <v>79647</v>
@@ -6057,19 +6057,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697413</v>
+        <v>697440</v>
       </c>
       <c r="R56" t="n">
-        <v>7312510</v>
+        <v>7312517</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6110,7 +6107,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6129,10 +6125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671934</v>
+        <v>127671928</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6140,34 +6136,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697440</v>
+        <v>697336</v>
       </c>
       <c r="R57" t="n">
-        <v>7312517</v>
+        <v>7312539</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6208,6 +6207,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B60" t="n">
-        <v>79108</v>
+        <v>97347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R60" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,7 +6499,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6511,39 +6510,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B61" t="n">
-        <v>97347</v>
+        <v>79108</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6553,10 +6552,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R61" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6597,6 +6596,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,17 +6608,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B62" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R62" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B63" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R63" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7314,48 +7314,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>91405</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R69" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7415,45 +7412,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B70" t="n">
-        <v>91405</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R70" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671945</v>
+        <v>127671972</v>
       </c>
       <c r="B71" t="n">
-        <v>57669</v>
+        <v>78435</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697270</v>
+        <v>697413</v>
       </c>
       <c r="R71" t="n">
-        <v>7312519</v>
+        <v>7312510</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7586,17 +7586,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>fodersök och påbörjad bohål</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7615,10 +7611,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671944</v>
+        <v>127671965</v>
       </c>
       <c r="B72" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7626,21 +7622,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7650,10 +7646,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697355</v>
+        <v>697325</v>
       </c>
       <c r="R72" t="n">
-        <v>7312481</v>
+        <v>7312536</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7686,11 +7682,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7717,10 +7708,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671972</v>
+        <v>127671945</v>
       </c>
       <c r="B73" t="n">
-        <v>78435</v>
+        <v>57669</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7728,21 +7719,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7752,10 +7743,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697413</v>
+        <v>697270</v>
       </c>
       <c r="R73" t="n">
-        <v>7312510</v>
+        <v>7312519</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7790,13 +7781,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7815,10 +7810,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671965</v>
+        <v>127671944</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7826,21 +7821,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7850,10 +7845,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697325</v>
+        <v>697355</v>
       </c>
       <c r="R74" t="n">
-        <v>7312536</v>
+        <v>7312481</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7886,6 +7881,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B49" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R49" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,7 +5411,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5423,39 +5422,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671958</v>
+        <v>127671964</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5465,10 +5464,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697325</v>
+        <v>697283</v>
       </c>
       <c r="R50" t="n">
-        <v>7312452</v>
+        <v>7312520</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5503,18 +5502,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5526,17 +5519,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127675520</v>
+        <v>127671970</v>
       </c>
       <c r="B51" t="n">
-        <v>79108</v>
+        <v>78696</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5544,39 +5537,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697413</v>
+        <v>697381</v>
       </c>
       <c r="R51" t="n">
-        <v>7312510</v>
+        <v>7312557</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5629,17 +5617,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671963</v>
+        <v>127675520</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5647,34 +5635,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697302</v>
+        <v>697413</v>
       </c>
       <c r="R52" t="n">
-        <v>7312488</v>
+        <v>7312510</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5715,6 +5708,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5733,32 +5727,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671964</v>
+        <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,10 +5762,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697283</v>
+        <v>697325</v>
       </c>
       <c r="R53" t="n">
-        <v>7312520</v>
+        <v>7312452</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5806,12 +5800,18 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7101,38 +7101,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127671938</v>
+        <v>127671959</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>697414</v>
+        <v>697355</v>
       </c>
       <c r="R67" t="n">
-        <v>7312503</v>
+        <v>7312481</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7189,6 +7189,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7207,38 +7208,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127671959</v>
+        <v>127671938</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7246,10 +7247,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697355</v>
+        <v>697414</v>
       </c>
       <c r="R68" t="n">
-        <v>7312481</v>
+        <v>7312503</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7286,7 +7287,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7295,7 +7296,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671963</v>
+        <v>127671970</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697302</v>
+        <v>697381</v>
       </c>
       <c r="R49" t="n">
-        <v>7312488</v>
+        <v>7312557</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,6 +5411,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5422,39 +5423,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671964</v>
+        <v>127671958</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5464,10 +5465,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697283</v>
+        <v>697325</v>
       </c>
       <c r="R50" t="n">
-        <v>7312520</v>
+        <v>7312452</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5502,12 +5503,18 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5519,17 +5526,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671970</v>
+        <v>127675520</v>
       </c>
       <c r="B51" t="n">
-        <v>78696</v>
+        <v>79108</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5537,34 +5544,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697381</v>
+        <v>697413</v>
       </c>
       <c r="R51" t="n">
-        <v>7312557</v>
+        <v>7312510</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5617,17 +5629,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127675520</v>
+        <v>127671963</v>
       </c>
       <c r="B52" t="n">
-        <v>79108</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5635,39 +5647,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697413</v>
+        <v>697302</v>
       </c>
       <c r="R52" t="n">
-        <v>7312510</v>
+        <v>7312488</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5708,7 +5715,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5727,32 +5733,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671958</v>
+        <v>127671964</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5762,10 +5768,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697325</v>
+        <v>697283</v>
       </c>
       <c r="R53" t="n">
-        <v>7312452</v>
+        <v>7312520</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5800,18 +5806,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B60" t="n">
-        <v>97347</v>
+        <v>79108</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R60" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,6 +6499,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6510,39 +6511,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B61" t="n">
-        <v>79108</v>
+        <v>97347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6552,10 +6553,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R61" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6596,7 +6597,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,17 +6608,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B62" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R62" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B63" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R63" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,49 +4239,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671947</v>
+        <v>127671948</v>
       </c>
       <c r="B38" t="n">
-        <v>57669</v>
+        <v>79115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697387</v>
+        <v>697440</v>
       </c>
       <c r="R38" t="n">
-        <v>7312552</v>
+        <v>7312523</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4316,17 +4312,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4338,52 +4330,56 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B39" t="n">
-        <v>79115</v>
+        <v>57669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R39" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4418,13 +4414,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671970</v>
+        <v>127671963</v>
       </c>
       <c r="B49" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697381</v>
+        <v>697302</v>
       </c>
       <c r="R49" t="n">
-        <v>7312557</v>
+        <v>7312488</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,7 +5411,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5423,39 +5422,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671958</v>
+        <v>127671964</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5465,10 +5464,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697325</v>
+        <v>697283</v>
       </c>
       <c r="R50" t="n">
-        <v>7312452</v>
+        <v>7312520</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5503,18 +5502,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5526,17 +5519,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127675520</v>
+        <v>127671970</v>
       </c>
       <c r="B51" t="n">
-        <v>79108</v>
+        <v>78696</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5544,39 +5537,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697413</v>
+        <v>697381</v>
       </c>
       <c r="R51" t="n">
-        <v>7312510</v>
+        <v>7312557</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5629,17 +5617,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671963</v>
+        <v>127675520</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5647,34 +5635,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697302</v>
+        <v>697413</v>
       </c>
       <c r="R52" t="n">
-        <v>7312488</v>
+        <v>7312510</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5715,6 +5708,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5733,32 +5727,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671964</v>
+        <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,10 +5762,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697283</v>
+        <v>697325</v>
       </c>
       <c r="R53" t="n">
-        <v>7312520</v>
+        <v>7312452</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5806,12 +5800,18 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B60" t="n">
-        <v>79108</v>
+        <v>97347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R60" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,7 +6499,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6511,39 +6510,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B61" t="n">
-        <v>97347</v>
+        <v>79108</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6553,10 +6552,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R61" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6597,6 +6596,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,17 +6608,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B62" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R62" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B63" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R63" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7101,38 +7101,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127671959</v>
+        <v>127671938</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>697355</v>
+        <v>697414</v>
       </c>
       <c r="R67" t="n">
-        <v>7312481</v>
+        <v>7312503</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7189,7 +7189,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7208,38 +7207,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127671938</v>
+        <v>127671959</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7247,10 +7246,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697414</v>
+        <v>697355</v>
       </c>
       <c r="R68" t="n">
-        <v>7312503</v>
+        <v>7312481</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7287,7 +7286,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7296,6 +7295,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -6615,10 +6615,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B62" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R62" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B63" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R63" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,45 +4239,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671948</v>
+        <v>127671947</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>57669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697440</v>
+        <v>697387</v>
       </c>
       <c r="R38" t="n">
-        <v>7312523</v>
+        <v>7312552</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4312,13 +4316,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4330,56 +4338,52 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671947</v>
+        <v>127671948</v>
       </c>
       <c r="B39" t="n">
-        <v>57669</v>
+        <v>79115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697387</v>
+        <v>697440</v>
       </c>
       <c r="R39" t="n">
-        <v>7312552</v>
+        <v>7312523</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4414,17 +4418,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671963</v>
+        <v>127671970</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5343,21 +5343,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697302</v>
+        <v>697381</v>
       </c>
       <c r="R49" t="n">
-        <v>7312488</v>
+        <v>7312557</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5411,6 +5411,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5422,39 +5423,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671964</v>
+        <v>127671958</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5464,10 +5465,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697283</v>
+        <v>697325</v>
       </c>
       <c r="R50" t="n">
-        <v>7312520</v>
+        <v>7312452</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5502,12 +5503,18 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5519,17 +5526,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671970</v>
+        <v>127675520</v>
       </c>
       <c r="B51" t="n">
-        <v>78696</v>
+        <v>79108</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5537,34 +5544,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697381</v>
+        <v>697413</v>
       </c>
       <c r="R51" t="n">
-        <v>7312557</v>
+        <v>7312510</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5617,17 +5629,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127675520</v>
+        <v>127671963</v>
       </c>
       <c r="B52" t="n">
-        <v>79108</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5635,39 +5647,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697413</v>
+        <v>697302</v>
       </c>
       <c r="R52" t="n">
-        <v>7312510</v>
+        <v>7312488</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5708,7 +5715,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5727,32 +5733,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671958</v>
+        <v>127671964</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5762,10 +5768,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697325</v>
+        <v>697283</v>
       </c>
       <c r="R53" t="n">
-        <v>7312452</v>
+        <v>7312520</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5800,18 +5806,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671932</v>
+        <v>127671928</v>
       </c>
       <c r="B54" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,34 +5841,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697427</v>
+        <v>697336</v>
       </c>
       <c r="R54" t="n">
-        <v>7312533</v>
+        <v>7312539</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5909,6 +5912,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5920,14 +5924,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127675495</v>
+        <v>127671932</v>
       </c>
       <c r="B55" t="n">
         <v>79647</v>
@@ -5956,19 +5960,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697413</v>
+        <v>697427</v>
       </c>
       <c r="R55" t="n">
-        <v>7312510</v>
+        <v>7312533</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6009,7 +6010,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127671934</v>
+        <v>127675495</v>
       </c>
       <c r="B56" t="n">
         <v>79647</v>
@@ -6057,16 +6057,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697440</v>
+        <v>697413</v>
       </c>
       <c r="R56" t="n">
-        <v>7312517</v>
+        <v>7312510</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6107,6 +6110,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6125,10 +6129,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671928</v>
+        <v>127671934</v>
       </c>
       <c r="B57" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6136,37 +6140,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697336</v>
+        <v>697440</v>
       </c>
       <c r="R57" t="n">
-        <v>7312539</v>
+        <v>7312517</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6207,7 +6208,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -4239,49 +4239,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671947</v>
+        <v>127671953</v>
       </c>
       <c r="B38" t="n">
-        <v>57669</v>
+        <v>97361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697387</v>
+        <v>697260</v>
       </c>
       <c r="R38" t="n">
-        <v>7312552</v>
+        <v>7312498</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4314,11 +4310,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>fodersök</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4348,7 +4339,7 @@
         <v>127671948</v>
       </c>
       <c r="B39" t="n">
-        <v>79115</v>
+        <v>79118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4443,45 +4434,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671953</v>
+        <v>127671947</v>
       </c>
       <c r="B40" t="n">
-        <v>97353</v>
+        <v>57670</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697260</v>
+        <v>697387</v>
       </c>
       <c r="R40" t="n">
-        <v>7312498</v>
+        <v>7312552</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4514,6 +4509,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4543,7 +4543,7 @@
         <v>127671935</v>
       </c>
       <c r="B41" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>127671968</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4734,32 +4734,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671941</v>
+        <v>127671954</v>
       </c>
       <c r="B43" t="n">
-        <v>56864</v>
+        <v>78791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697421</v>
+        <v>697348</v>
       </c>
       <c r="R43" t="n">
-        <v>7312530</v>
+        <v>7312527</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4807,17 +4807,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4839,7 +4835,7 @@
         <v>127671939</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4942,32 +4938,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671954</v>
+        <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>56864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4977,10 +4973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697348</v>
+        <v>697421</v>
       </c>
       <c r="R45" t="n">
-        <v>7312527</v>
+        <v>7312530</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5015,13 +5011,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671957</v>
+        <v>127671962</v>
       </c>
       <c r="B46" t="n">
-        <v>78787</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,21 +5051,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>697236</v>
+        <v>697316</v>
       </c>
       <c r="R46" t="n">
-        <v>7312490</v>
+        <v>7312471</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671962</v>
+        <v>127671957</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>78790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5148,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697316</v>
+        <v>697236</v>
       </c>
       <c r="R47" t="n">
-        <v>7312471</v>
+        <v>7312490</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5237,7 +5237,7 @@
         <v>127671955</v>
       </c>
       <c r="B48" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>127671970</v>
       </c>
       <c r="B49" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5430,32 +5430,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671958</v>
+        <v>127671963</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697325</v>
+        <v>697302</v>
       </c>
       <c r="R50" t="n">
-        <v>7312452</v>
+        <v>7312488</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5503,18 +5503,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5526,17 +5520,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127675520</v>
+        <v>127671964</v>
       </c>
       <c r="B51" t="n">
-        <v>79108</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5544,39 +5538,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697413</v>
+        <v>697283</v>
       </c>
       <c r="R51" t="n">
-        <v>7312510</v>
+        <v>7312520</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5617,7 +5606,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5636,10 +5624,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671963</v>
+        <v>127675520</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5647,34 +5635,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697302</v>
+        <v>697413</v>
       </c>
       <c r="R52" t="n">
-        <v>7312488</v>
+        <v>7312510</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5715,6 +5708,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5733,32 +5727,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671964</v>
+        <v>127671958</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,10 +5762,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697283</v>
+        <v>697325</v>
       </c>
       <c r="R53" t="n">
-        <v>7312520</v>
+        <v>7312452</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5806,12 +5800,18 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5833,7 +5833,7 @@
         <v>127671928</v>
       </c>
       <c r="B54" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>127671932</v>
       </c>
       <c r="B55" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>127675495</v>
       </c>
       <c r="B56" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>127671934</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>127671929</v>
       </c>
       <c r="B58" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>127671974</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6420,32 +6420,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671952</v>
+        <v>127671960</v>
       </c>
       <c r="B60" t="n">
-        <v>97347</v>
+        <v>79111</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>864</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697273</v>
+        <v>697356</v>
       </c>
       <c r="R60" t="n">
-        <v>7312509</v>
+        <v>7312567</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6499,6 +6499,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6510,39 +6511,39 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671960</v>
+        <v>127671952</v>
       </c>
       <c r="B61" t="n">
-        <v>79108</v>
+        <v>97355</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6552,10 +6553,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697356</v>
+        <v>697273</v>
       </c>
       <c r="R61" t="n">
-        <v>7312567</v>
+        <v>7312509</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6596,7 +6597,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6608,17 +6608,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671936</v>
+        <v>127671931</v>
       </c>
       <c r="B62" t="n">
-        <v>79618</v>
+        <v>79650</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6650,10 +6650,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697281</v>
+        <v>697282</v>
       </c>
       <c r="R62" t="n">
-        <v>7312520</v>
+        <v>7312524</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6712,10 +6712,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671931</v>
+        <v>127671936</v>
       </c>
       <c r="B63" t="n">
-        <v>79647</v>
+        <v>79621</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,21 +6723,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697282</v>
+        <v>697281</v>
       </c>
       <c r="R63" t="n">
-        <v>7312524</v>
+        <v>7312520</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127671930</v>
+        <v>127671961</v>
       </c>
       <c r="B64" t="n">
-        <v>79647</v>
+        <v>79111</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,21 +6820,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>697297</v>
+        <v>697347</v>
       </c>
       <c r="R64" t="n">
-        <v>7312471</v>
+        <v>7312562</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6888,6 +6888,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6899,17 +6900,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127671961</v>
+        <v>127671930</v>
       </c>
       <c r="B65" t="n">
-        <v>79108</v>
+        <v>79650</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6917,21 +6918,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6941,10 +6942,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>697347</v>
+        <v>697297</v>
       </c>
       <c r="R65" t="n">
-        <v>7312562</v>
+        <v>7312471</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6985,7 +6986,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7007,7 +7007,7 @@
         <v>127671969</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7101,38 +7101,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127671938</v>
+        <v>127671959</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>697414</v>
+        <v>697355</v>
       </c>
       <c r="R67" t="n">
-        <v>7312503</v>
+        <v>7312481</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7189,6 +7189,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7207,38 +7208,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127671959</v>
+        <v>127671938</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7246,10 +7247,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697355</v>
+        <v>697414</v>
       </c>
       <c r="R68" t="n">
-        <v>7312481</v>
+        <v>7312503</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7286,7 +7287,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7295,7 +7296,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7314,45 +7314,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127671973</v>
+        <v>127675593</v>
       </c>
       <c r="B69" t="n">
-        <v>91405</v>
+        <v>79032</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697309</v>
+        <v>697356</v>
       </c>
       <c r="R69" t="n">
-        <v>7312479</v>
+        <v>7312567</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7412,48 +7415,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127675593</v>
+        <v>127671973</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>91413</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697356</v>
+        <v>697309</v>
       </c>
       <c r="R70" t="n">
-        <v>7312567</v>
+        <v>7312479</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7516,7 +7516,7 @@
         <v>127671972</v>
       </c>
       <c r="B71" t="n">
-        <v>78435</v>
+        <v>78438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>127671965</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>127671945</v>
       </c>
       <c r="B73" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>127671944</v>
       </c>
       <c r="B74" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>127671951</v>
       </c>
       <c r="B75" t="n">
-        <v>105493</v>
+        <v>105501</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>127705223</v>
       </c>
       <c r="B76" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -5040,10 +5040,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671962</v>
+        <v>127671957</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>78790</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,21 +5051,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>697316</v>
+        <v>697236</v>
       </c>
       <c r="R46" t="n">
-        <v>7312471</v>
+        <v>7312490</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5137,7 +5137,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671957</v>
+        <v>127671955</v>
       </c>
       <c r="B47" t="n">
         <v>78790</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697236</v>
+        <v>697329</v>
       </c>
       <c r="R47" t="n">
-        <v>7312490</v>
+        <v>7312476</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5216,6 +5216,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5227,17 +5228,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127671955</v>
+        <v>127671962</v>
       </c>
       <c r="B48" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5245,21 +5246,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5269,10 +5270,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>697329</v>
+        <v>697316</v>
       </c>
       <c r="R48" t="n">
-        <v>7312476</v>
+        <v>7312471</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5313,7 +5314,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5325,39 +5325,39 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671970</v>
+        <v>127671958</v>
       </c>
       <c r="B49" t="n">
-        <v>78699</v>
+        <v>98478</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697381</v>
+        <v>697325</v>
       </c>
       <c r="R49" t="n">
-        <v>7312557</v>
+        <v>7312452</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5403,6 +5403,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5430,10 +5435,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671963</v>
+        <v>127671970</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5441,21 +5446,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5465,10 +5470,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697302</v>
+        <v>697381</v>
       </c>
       <c r="R50" t="n">
-        <v>7312488</v>
+        <v>7312557</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5509,6 +5514,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5520,14 +5526,14 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671964</v>
+        <v>127671963</v>
       </c>
       <c r="B51" t="n">
         <v>79032</v>
@@ -5562,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697283</v>
+        <v>697302</v>
       </c>
       <c r="R51" t="n">
-        <v>7312520</v>
+        <v>7312488</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5624,10 +5630,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127675520</v>
+        <v>127671964</v>
       </c>
       <c r="B52" t="n">
-        <v>79111</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5635,39 +5641,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697413</v>
+        <v>697283</v>
       </c>
       <c r="R52" t="n">
-        <v>7312510</v>
+        <v>7312520</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5708,7 +5709,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5727,45 +5727,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127671958</v>
+        <v>127675520</v>
       </c>
       <c r="B53" t="n">
-        <v>98478</v>
+        <v>79111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697325</v>
+        <v>697413</v>
       </c>
       <c r="R53" t="n">
-        <v>7312452</v>
+        <v>7312510</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5800,11 +5805,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7513,10 +7513,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671972</v>
+        <v>127671965</v>
       </c>
       <c r="B71" t="n">
-        <v>78438</v>
+        <v>79032</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7524,21 +7524,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697413</v>
+        <v>697325</v>
       </c>
       <c r="R71" t="n">
-        <v>7312510</v>
+        <v>7312536</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7592,7 +7592,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7611,10 +7610,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671965</v>
+        <v>127671945</v>
       </c>
       <c r="B72" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7622,21 +7621,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7646,10 +7645,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697325</v>
+        <v>697270</v>
       </c>
       <c r="R72" t="n">
-        <v>7312536</v>
+        <v>7312519</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7682,6 +7681,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7708,7 +7712,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671945</v>
+        <v>127671944</v>
       </c>
       <c r="B73" t="n">
         <v>57670</v>
@@ -7743,10 +7747,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>697270</v>
+        <v>697355</v>
       </c>
       <c r="R73" t="n">
-        <v>7312519</v>
+        <v>7312481</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7783,7 +7787,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>fodersök och påbörjad bohål</t>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7810,10 +7814,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671944</v>
+        <v>127671972</v>
       </c>
       <c r="B74" t="n">
-        <v>57670</v>
+        <v>78438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7821,21 +7825,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7845,10 +7849,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697355</v>
+        <v>697413</v>
       </c>
       <c r="R74" t="n">
-        <v>7312481</v>
+        <v>7312510</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7883,17 +7887,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>fodersök</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -8013,7 +8013,7 @@
         <v>127705223</v>
       </c>
       <c r="B76" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -3452,7 +3452,7 @@
         <v>126801482</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>126801481</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>79600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>126801479</v>
       </c>
       <c r="B32" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>126801483</v>
       </c>
       <c r="B33" t="n">
-        <v>57658</v>
+        <v>57654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>126801486</v>
       </c>
       <c r="B34" t="n">
-        <v>78424</v>
+        <v>78417</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>126801480</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>126801485</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>126801484</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>126387763</v>
       </c>
       <c r="B9" t="n">
-        <v>56849</v>
+        <v>57073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>126387761</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>57073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>56864</v>
+        <v>57073</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>126387763</v>
       </c>
       <c r="B9" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>126387761</v>
       </c>
       <c r="B13" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>126387763</v>
       </c>
       <c r="B9" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>126387761</v>
       </c>
       <c r="B13" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>126387763</v>
       </c>
       <c r="B9" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>126387761</v>
       </c>
       <c r="B13" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>126387763</v>
       </c>
       <c r="B9" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>126387761</v>
       </c>
       <c r="B13" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>127671941</v>
       </c>
       <c r="B45" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8124,6 +8124,229 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>133234359</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79334</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>697327</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7312439</v>
+      </c>
+      <c r="S77" t="n">
+        <v>7</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133233913</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>697333</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7312440</v>
+      </c>
+      <c r="S78" t="n">
+        <v>6</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -8129,7 +8129,7 @@
         <v>133234359</v>
       </c>
       <c r="B77" t="n">
-        <v>79334</v>
+        <v>79335</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>133233913</v>
       </c>
       <c r="B78" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -8236,7 +8236,7 @@
         <v>133233913</v>
       </c>
       <c r="B78" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126387773</v>
+        <v>126387774</v>
       </c>
       <c r="B2" t="n">
-        <v>91406</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697446</v>
+        <v>697650</v>
       </c>
       <c r="R2" t="n">
-        <v>7312463</v>
+        <v>7312428</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,48 +776,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126387767</v>
+        <v>126017340</v>
       </c>
       <c r="B3" t="n">
-        <v>92727</v>
+        <v>99007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>233</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697567</v>
+        <v>697486</v>
       </c>
       <c r="R3" t="n">
-        <v>7312415</v>
+        <v>7312379</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +845,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +870,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126387768</v>
+        <v>126387775</v>
       </c>
       <c r="B4" t="n">
-        <v>92727</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697557</v>
+        <v>697546</v>
       </c>
       <c r="R4" t="n">
-        <v>7312419</v>
+        <v>7312408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -948,6 +961,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126387769</v>
+        <v>126801482</v>
       </c>
       <c r="B5" t="n">
-        <v>92727</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +991,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697652</v>
+        <v>697322</v>
       </c>
       <c r="R5" t="n">
-        <v>7312419</v>
+        <v>7312321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1077,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126387770</v>
+        <v>126387772</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697631</v>
+        <v>697650</v>
       </c>
       <c r="R6" t="n">
-        <v>7312437</v>
+        <v>7312428</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126387775</v>
+        <v>126387767</v>
       </c>
       <c r="B7" t="n">
-        <v>78647</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697546</v>
+        <v>697567</v>
       </c>
       <c r="R7" t="n">
-        <v>7312408</v>
+        <v>7312415</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1239,7 +1253,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126387766</v>
+        <v>126387768</v>
       </c>
       <c r="B8" t="n">
-        <v>75075</v>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1269,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697603</v>
+        <v>697557</v>
       </c>
       <c r="R8" t="n">
-        <v>7312452</v>
+        <v>7312419</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1350,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1356,49 +1368,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126387763</v>
+        <v>126387769</v>
       </c>
       <c r="B9" t="n">
-        <v>57092</v>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697614</v>
+        <v>697652</v>
       </c>
       <c r="R9" t="n">
-        <v>7312438</v>
+        <v>7312419</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,11 +1439,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1462,53 +1465,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126387765</v>
+        <v>126801486</v>
       </c>
       <c r="B10" t="n">
-        <v>58027</v>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>697472</v>
+        <v>697280</v>
       </c>
       <c r="R10" t="n">
-        <v>7312435</v>
+        <v>7312337</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,12 +1530,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1567,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126387772</v>
+        <v>126801483</v>
       </c>
       <c r="B11" t="n">
-        <v>91406</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>697650</v>
+        <v>697264</v>
       </c>
       <c r="R11" t="n">
-        <v>7312428</v>
+        <v>7312393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1632,12 +1627,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126387771</v>
+        <v>126801484</v>
       </c>
       <c r="B12" t="n">
-        <v>79059</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1670,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697390</v>
+        <v>697426</v>
       </c>
       <c r="R12" t="n">
-        <v>7312543</v>
+        <v>7312385</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1729,12 +1724,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1764,7 +1764,7 @@
         <v>126387761</v>
       </c>
       <c r="B13" t="n">
-        <v>57092</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,48 +1867,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126387776</v>
+        <v>126379706</v>
       </c>
       <c r="B14" t="n">
-        <v>92535</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>697723</v>
+        <v>697491</v>
       </c>
       <c r="R14" t="n">
-        <v>7312440</v>
+        <v>7312377</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1932,12 +1936,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1952,60 +1961,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126429379</v>
+        <v>126379707</v>
       </c>
       <c r="B15" t="n">
-        <v>92727</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697344</v>
+        <v>697510</v>
       </c>
       <c r="R15" t="n">
-        <v>7312456</v>
+        <v>7312392</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2029,12 +2042,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,63 +2067,64 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126387774</v>
+        <v>126379709</v>
       </c>
       <c r="B16" t="n">
-        <v>91506</v>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697650</v>
+        <v>697518</v>
       </c>
       <c r="R16" t="n">
-        <v>7312428</v>
+        <v>7312397</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2129,12 +2148,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2143,71 +2167,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126441134</v>
+        <v>126801481</v>
       </c>
       <c r="B17" t="n">
-        <v>105381</v>
+        <v>79917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+          <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>697636</v>
+        <v>697289</v>
       </c>
       <c r="R17" t="n">
-        <v>7312436</v>
+        <v>7312348</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2231,12 +2250,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2245,71 +2264,69 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126441319</v>
+        <v>127671928</v>
       </c>
       <c r="B18" t="n">
-        <v>98382</v>
+        <v>79359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+          <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>697393</v>
+        <v>697336</v>
       </c>
       <c r="R18" t="n">
-        <v>7312461</v>
+        <v>7312539</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2333,12 +2350,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,60 +2371,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126429376</v>
+        <v>126379715</v>
       </c>
       <c r="B19" t="n">
-        <v>79569</v>
+        <v>99007</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>233</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>697266</v>
+        <v>697008</v>
       </c>
       <c r="R19" t="n">
-        <v>7312481</v>
+        <v>7312540</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2431,12 +2452,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2451,64 +2477,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126440996</v>
+        <v>127671970</v>
       </c>
       <c r="B20" t="n">
-        <v>97245</v>
+        <v>78993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+          <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>697636</v>
+        <v>697381</v>
       </c>
       <c r="R20" t="n">
-        <v>7312436</v>
+        <v>7312557</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2532,12 +2554,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,44 +2575,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126429374</v>
+        <v>126387771</v>
       </c>
       <c r="B21" t="n">
-        <v>105381</v>
+        <v>79406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2600,10 +2622,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697354</v>
+        <v>697390</v>
       </c>
       <c r="R21" t="n">
-        <v>7312456</v>
+        <v>7312543</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2630,12 +2652,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2644,7 +2666,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2684,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126429382</v>
+        <v>127671960</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2674,21 +2695,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2698,13 +2719,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>697632</v>
+        <v>697356</v>
       </c>
       <c r="R22" t="n">
-        <v>7312442</v>
+        <v>7312567</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2728,12 +2749,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,6 +2763,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2753,17 +2775,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126429384</v>
+        <v>127671961</v>
       </c>
       <c r="B23" t="n">
-        <v>78386</v>
+        <v>79406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2771,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2795,13 +2817,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697375</v>
+        <v>697347</v>
       </c>
       <c r="R23" t="n">
-        <v>7312460</v>
+        <v>7312562</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2825,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,6 +2861,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2850,17 +2873,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126429375</v>
+        <v>127675520</v>
       </c>
       <c r="B24" t="n">
-        <v>79598</v>
+        <v>79406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,37 +2891,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697253</v>
+        <v>697413</v>
       </c>
       <c r="R24" t="n">
-        <v>7312498</v>
+        <v>7312510</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2922,12 +2950,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2936,6 +2964,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2954,10 +2983,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126429381</v>
+        <v>126429377</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2965,21 +2994,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2989,10 +3018,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>697306</v>
+        <v>697256</v>
       </c>
       <c r="R25" t="n">
-        <v>7312454</v>
+        <v>7312452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,32 +3080,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126429383</v>
+        <v>126387773</v>
       </c>
       <c r="B26" t="n">
-        <v>77929</v>
+        <v>92083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3086,10 +3115,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697242</v>
+        <v>697446</v>
       </c>
       <c r="R26" t="n">
-        <v>7312477</v>
+        <v>7312463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3116,12 +3145,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3148,52 +3177,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126441004</v>
+        <v>126429379</v>
       </c>
       <c r="B27" t="n">
-        <v>97242</v>
+        <v>91962</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221946</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+          <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697636</v>
+        <v>697344</v>
       </c>
       <c r="R27" t="n">
-        <v>7312436</v>
+        <v>7312456</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3231,29 +3256,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126429377</v>
+        <v>126387776</v>
       </c>
       <c r="B28" t="n">
-        <v>91245</v>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3261,21 +3285,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3285,10 +3309,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697256</v>
+        <v>697723</v>
       </c>
       <c r="R28" t="n">
-        <v>7312452</v>
+        <v>7312440</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,12 +3339,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3347,10 +3371,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126441387</v>
+        <v>127671973</v>
       </c>
       <c r="B29" t="n">
-        <v>97245</v>
+        <v>91966</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3358,41 +3382,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>5321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+          <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697258</v>
+        <v>697309</v>
       </c>
       <c r="R29" t="n">
-        <v>7312485</v>
+        <v>7312479</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3416,12 +3436,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3437,44 +3457,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126801482</v>
+        <v>126801479</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3484,10 +3504,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>697322</v>
+        <v>697369</v>
       </c>
       <c r="R30" t="n">
-        <v>7312321</v>
+        <v>7312442</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,32 +3566,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126801481</v>
+        <v>126429381</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3601,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697289</v>
+        <v>697306</v>
       </c>
       <c r="R31" t="n">
-        <v>7312348</v>
+        <v>7312454</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3611,12 +3631,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3643,32 +3663,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126801479</v>
+        <v>126429382</v>
       </c>
       <c r="B32" t="n">
-        <v>91295</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3678,7 +3698,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697369</v>
+        <v>697632</v>
       </c>
       <c r="R32" t="n">
         <v>7312442</v>
@@ -3708,12 +3728,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3740,32 +3760,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126801483</v>
+        <v>127671962</v>
       </c>
       <c r="B33" t="n">
-        <v>57658</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3775,13 +3795,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>697264</v>
+        <v>697316</v>
       </c>
       <c r="R33" t="n">
-        <v>7312393</v>
+        <v>7312471</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3805,12 +3825,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3837,32 +3857,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126801486</v>
+        <v>127671963</v>
       </c>
       <c r="B34" t="n">
-        <v>78424</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3872,13 +3892,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>697280</v>
+        <v>697302</v>
       </c>
       <c r="R34" t="n">
-        <v>7312337</v>
+        <v>7312488</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3902,12 +3922,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3934,32 +3954,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126801480</v>
+        <v>127671964</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3969,13 +3989,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>697258</v>
+        <v>697283</v>
       </c>
       <c r="R35" t="n">
-        <v>7312452</v>
+        <v>7312520</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3999,12 +4019,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4031,52 +4051,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126801485</v>
+        <v>127671965</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>697432</v>
+        <v>697325</v>
       </c>
       <c r="R36" t="n">
-        <v>7312599</v>
+        <v>7312536</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4100,17 +4116,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>bohål</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4137,32 +4148,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126801484</v>
+        <v>127671968</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4172,13 +4183,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>697426</v>
+        <v>697330</v>
       </c>
       <c r="R37" t="n">
-        <v>7312385</v>
+        <v>7312575</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4202,17 +4213,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4239,32 +4245,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127671953</v>
+        <v>127671969</v>
       </c>
       <c r="B38" t="n">
-        <v>97361</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4274,10 +4280,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697260</v>
+        <v>697347</v>
       </c>
       <c r="R38" t="n">
-        <v>7312498</v>
+        <v>7312584</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4336,45 +4342,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127671948</v>
+        <v>127675593</v>
       </c>
       <c r="B39" t="n">
-        <v>79118</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697440</v>
+        <v>697356</v>
       </c>
       <c r="R39" t="n">
-        <v>7312523</v>
+        <v>7312567</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4427,17 +4436,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Steve Daurer, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127671947</v>
+        <v>126429384</v>
       </c>
       <c r="B40" t="n">
-        <v>57670</v>
+        <v>78730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4445,41 +4454,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697387</v>
+        <v>697375</v>
       </c>
       <c r="R40" t="n">
-        <v>7312552</v>
+        <v>7312460</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4503,17 +4508,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>fodersök</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4540,10 +4540,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127671935</v>
+        <v>127671972</v>
       </c>
       <c r="B41" t="n">
-        <v>79650</v>
+        <v>78730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4551,21 +4551,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697439</v>
+        <v>697413</v>
       </c>
       <c r="R41" t="n">
-        <v>7312528</v>
+        <v>7312510</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4619,6 +4619,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4637,10 +4638,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127671968</v>
+        <v>126387766</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4648,21 +4649,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4672,13 +4673,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>697330</v>
+        <v>697603</v>
       </c>
       <c r="R42" t="n">
-        <v>7312575</v>
+        <v>7312452</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4702,12 +4703,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4716,6 +4717,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4734,10 +4736,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127671954</v>
+        <v>127671955</v>
       </c>
       <c r="B43" t="n">
-        <v>78791</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4745,21 +4747,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4769,10 +4771,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697348</v>
+        <v>697329</v>
       </c>
       <c r="R43" t="n">
-        <v>7312527</v>
+        <v>7312476</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4825,17 +4827,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127671939</v>
+        <v>127671957</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4843,38 +4845,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>697265</v>
+        <v>697236</v>
       </c>
       <c r="R44" t="n">
-        <v>7312540</v>
+        <v>7312490</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4909,11 +4907,6 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -4931,39 +4924,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127671941</v>
+        <v>127671948</v>
       </c>
       <c r="B45" t="n">
-        <v>57092</v>
+        <v>79413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6450</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4973,10 +4966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>697421</v>
+        <v>697440</v>
       </c>
       <c r="R45" t="n">
-        <v>7312530</v>
+        <v>7312523</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5011,17 +5004,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5033,17 +5022,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127671957</v>
+        <v>126429375</v>
       </c>
       <c r="B46" t="n">
-        <v>78790</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,21 +5040,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5075,13 +5064,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>697236</v>
+        <v>697253</v>
       </c>
       <c r="R46" t="n">
-        <v>7312490</v>
+        <v>7312498</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5105,12 +5094,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5137,10 +5126,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127671955</v>
+        <v>126801480</v>
       </c>
       <c r="B47" t="n">
-        <v>78790</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,21 +5137,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5172,13 +5161,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697329</v>
+        <v>697258</v>
       </c>
       <c r="R47" t="n">
-        <v>7312476</v>
+        <v>7312452</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5202,12 +5191,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5216,7 +5205,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5228,17 +5216,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127671962</v>
+        <v>127671929</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5246,21 +5234,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5270,10 +5258,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>697316</v>
+        <v>697349</v>
       </c>
       <c r="R48" t="n">
-        <v>7312471</v>
+        <v>7312528</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5332,32 +5320,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127671958</v>
+        <v>127671930</v>
       </c>
       <c r="B49" t="n">
-        <v>98478</v>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5367,10 +5355,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>697325</v>
+        <v>697297</v>
       </c>
       <c r="R49" t="n">
-        <v>7312452</v>
+        <v>7312471</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5405,18 +5393,12 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5428,17 +5410,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127671970</v>
+        <v>127671931</v>
       </c>
       <c r="B50" t="n">
-        <v>78699</v>
+        <v>79946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5446,21 +5428,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5470,10 +5452,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>697381</v>
+        <v>697282</v>
       </c>
       <c r="R50" t="n">
-        <v>7312557</v>
+        <v>7312524</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5514,7 +5496,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5526,17 +5507,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127671963</v>
+        <v>127671932</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5544,21 +5525,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5568,10 +5549,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>697302</v>
+        <v>697427</v>
       </c>
       <c r="R51" t="n">
-        <v>7312488</v>
+        <v>7312533</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5630,10 +5611,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127671964</v>
+        <v>127671934</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>79946</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5641,21 +5622,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5665,10 +5646,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>697283</v>
+        <v>697440</v>
       </c>
       <c r="R52" t="n">
-        <v>7312520</v>
+        <v>7312517</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5727,10 +5708,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127675520</v>
+        <v>127671935</v>
       </c>
       <c r="B53" t="n">
-        <v>79111</v>
+        <v>79946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5738,39 +5719,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>697413</v>
+        <v>697439</v>
       </c>
       <c r="R53" t="n">
-        <v>7312510</v>
+        <v>7312528</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5811,7 +5787,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5830,10 +5805,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127671928</v>
+        <v>127671974</v>
       </c>
       <c r="B54" t="n">
-        <v>79064</v>
+        <v>79946</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5841,37 +5816,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>697336</v>
+        <v>697240</v>
       </c>
       <c r="R54" t="n">
-        <v>7312539</v>
+        <v>7312489</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5912,7 +5884,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -5924,17 +5895,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127671932</v>
+        <v>127675495</v>
       </c>
       <c r="B55" t="n">
-        <v>79650</v>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5960,16 +5931,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>697427</v>
+        <v>697413</v>
       </c>
       <c r="R55" t="n">
-        <v>7312533</v>
+        <v>7312510</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6010,6 +5984,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6028,10 +6003,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127675495</v>
+        <v>126429383</v>
       </c>
       <c r="B56" t="n">
-        <v>79650</v>
+        <v>78334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6039,40 +6014,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>697413</v>
+        <v>697242</v>
       </c>
       <c r="R56" t="n">
-        <v>7312510</v>
+        <v>7312477</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6096,12 +6068,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6110,7 +6082,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6129,32 +6100,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127671934</v>
+        <v>127671944</v>
       </c>
       <c r="B57" t="n">
-        <v>79650</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6164,10 +6135,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>697440</v>
+        <v>697355</v>
       </c>
       <c r="R57" t="n">
-        <v>7312517</v>
+        <v>7312481</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6200,6 +6171,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6226,32 +6202,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127671929</v>
+        <v>127671945</v>
       </c>
       <c r="B58" t="n">
-        <v>79650</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6261,10 +6237,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>697349</v>
+        <v>697270</v>
       </c>
       <c r="R58" t="n">
-        <v>7312528</v>
+        <v>7312519</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6297,6 +6273,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>fodersök och påbörjad bohål</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6323,45 +6304,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127671974</v>
+        <v>127671946</v>
       </c>
       <c r="B59" t="n">
-        <v>79650</v>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>697240</v>
+        <v>697474</v>
       </c>
       <c r="R59" t="n">
-        <v>7312489</v>
+        <v>7312544</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6394,6 +6379,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>fodersök</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6420,45 +6410,49 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127671960</v>
+        <v>127671947</v>
       </c>
       <c r="B60" t="n">
-        <v>79111</v>
+        <v>57950</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>697356</v>
+        <v>697387</v>
       </c>
       <c r="R60" t="n">
-        <v>7312567</v>
+        <v>7312552</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6493,13 +6487,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>fodersök</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6511,55 +6509,59 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127671952</v>
+        <v>126801485</v>
       </c>
       <c r="B61" t="n">
-        <v>97355</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>697273</v>
+        <v>697432</v>
       </c>
       <c r="R61" t="n">
-        <v>7312509</v>
+        <v>7312599</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6583,12 +6585,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>bohål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6615,10 +6622,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127671931</v>
+        <v>127671938</v>
       </c>
       <c r="B62" t="n">
-        <v>79650</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6626,34 +6633,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>697282</v>
+        <v>697414</v>
       </c>
       <c r="R62" t="n">
-        <v>7312524</v>
+        <v>7312503</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6688,6 +6699,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6705,17 +6721,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127671936</v>
+        <v>127671939</v>
       </c>
       <c r="B63" t="n">
-        <v>79621</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6723,34 +6739,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697281</v>
+        <v>697265</v>
       </c>
       <c r="R63" t="n">
-        <v>7312520</v>
+        <v>7312540</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6785,6 +6805,11 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -6802,17 +6827,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127671961</v>
+        <v>127705223</v>
       </c>
       <c r="B64" t="n">
-        <v>79111</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6820,34 +6845,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>697347</v>
+        <v>697435</v>
       </c>
       <c r="R64" t="n">
-        <v>7312562</v>
+        <v>7312514</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6877,18 +6906,32 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6907,48 +6950,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127671930</v>
+        <v>126387763</v>
       </c>
       <c r="B65" t="n">
-        <v>79650</v>
+        <v>57141</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>697297</v>
+        <v>697614</v>
       </c>
       <c r="R65" t="n">
-        <v>7312471</v>
+        <v>7312438</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6972,12 +7019,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7004,32 +7056,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127671969</v>
+        <v>127671941</v>
       </c>
       <c r="B66" t="n">
-        <v>79032</v>
+        <v>57141</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7039,10 +7091,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>697347</v>
+        <v>697421</v>
       </c>
       <c r="R66" t="n">
-        <v>7312584</v>
+        <v>7312530</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7075,6 +7127,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7101,52 +7158,56 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127671959</v>
+        <v>126387765</v>
       </c>
       <c r="B67" t="n">
-        <v>98478</v>
+        <v>58327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>697355</v>
+        <v>697472</v>
       </c>
       <c r="R67" t="n">
-        <v>7312481</v>
+        <v>7312435</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7170,17 +7231,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7189,7 +7245,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7201,56 +7256,56 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127671938</v>
+        <v>126379710</v>
       </c>
       <c r="B68" t="n">
-        <v>57673</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697414</v>
+        <v>697188</v>
       </c>
       <c r="R68" t="n">
-        <v>7312503</v>
+        <v>7312721</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7277,17 +7332,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7302,60 +7357,61 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127675593</v>
+        <v>126379711</v>
       </c>
       <c r="B69" t="n">
-        <v>79032</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>697356</v>
+        <v>697094</v>
       </c>
       <c r="R69" t="n">
-        <v>7312567</v>
+        <v>7312700</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7382,12 +7438,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7396,64 +7457,67 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127671973</v>
+        <v>126379712</v>
       </c>
       <c r="B70" t="n">
-        <v>91413</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>697309</v>
+        <v>697081</v>
       </c>
       <c r="R70" t="n">
-        <v>7312479</v>
+        <v>7312657</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7480,12 +7544,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7494,64 +7563,67 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127671965</v>
+        <v>126379716</v>
       </c>
       <c r="B71" t="n">
-        <v>79032</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Moskosel, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>697325</v>
+        <v>697028</v>
       </c>
       <c r="R71" t="n">
-        <v>7312536</v>
+        <v>7312554</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7578,12 +7650,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7598,44 +7675,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127671945</v>
+        <v>127671958</v>
       </c>
       <c r="B72" t="n">
-        <v>57670</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7645,10 +7722,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697270</v>
+        <v>697325</v>
       </c>
       <c r="R72" t="n">
-        <v>7312519</v>
+        <v>7312452</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7685,7 +7762,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>fodersök och påbörjad bohål</t>
+          <t>Troligtvis finns det fler växtplater men svårt upptäckt under blåbärsris</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7694,6 +7771,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7705,42 +7783,46 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127671944</v>
+        <v>127671959</v>
       </c>
       <c r="B73" t="n">
-        <v>57670</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
@@ -7787,7 +7869,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>fodersök</t>
+          <t>flertal knärötter som var svara att upptäcka under bärriset</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7796,6 +7878,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7807,55 +7890,64 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Heike Kontermann, Steve Daurer</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127671972</v>
+        <v>133233913</v>
       </c>
       <c r="B74" t="n">
-        <v>78438</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Skuorrejaureberget, Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>697413</v>
+        <v>697333</v>
       </c>
       <c r="R74" t="n">
-        <v>7312510</v>
+        <v>7312440</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7879,12 +7971,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7893,7 +7995,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7912,48 +8013,48 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127671951</v>
+        <v>133235530</v>
       </c>
       <c r="B75" t="n">
-        <v>105501</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Pi lm</t>
+          <t>Skuorrejaureberget, Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>697331</v>
+        <v>697037</v>
       </c>
       <c r="R75" t="n">
-        <v>7312443</v>
+        <v>7312551</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7977,12 +8078,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7991,7 +8102,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8010,52 +8120,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127705223</v>
+        <v>126429374</v>
       </c>
       <c r="B76" t="n">
-        <v>57684</v>
+        <v>106229</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>697435</v>
+        <v>697354</v>
       </c>
       <c r="R76" t="n">
-        <v>7312514</v>
+        <v>7312456</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8079,27 +8185,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8108,6 +8199,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8119,55 +8211,59 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Heike Kontermann, Steve Daurer</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133234359</v>
+        <v>126441134</v>
       </c>
       <c r="B77" t="n">
-        <v>79360</v>
+        <v>106229</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>230405</v>
+        <v>221725</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Skuorrejaureberget, Pi lm</t>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>697327</v>
+        <v>697636</v>
       </c>
       <c r="R77" t="n">
-        <v>7312439</v>
+        <v>7312436</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8191,22 +8287,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8215,75 +8301,67 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133233913</v>
+        <v>127671951</v>
       </c>
       <c r="B78" t="n">
-        <v>99181</v>
+        <v>106229</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Skuorrejaureberget, Skuorrejaureberget, Pi lm</t>
+          <t>Skuorrejaureberget, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>697333</v>
+        <v>697331</v>
       </c>
       <c r="R78" t="n">
-        <v>7312440</v>
+        <v>7312443</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8307,22 +8385,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8331,6 +8399,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8346,6 +8415,1104 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126440996</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>697636</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7312436</v>
+      </c>
+      <c r="S79" t="n">
+        <v>50</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126441387</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>697258</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7312485</v>
+      </c>
+      <c r="S80" t="n">
+        <v>50</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127671953</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>697260</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7312498</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127671952</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>697273</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7312509</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126441004</v>
+      </c>
+      <c r="B83" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>697636</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7312436</v>
+      </c>
+      <c r="S83" t="n">
+        <v>50</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126441319</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Skuorrejaurberget, östra delen, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>697393</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7312461</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Maria Marklund, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126387770</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>697631</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7312437</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127671954</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>697348</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7312527</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126429376</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>697266</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7312481</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127671936</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>697281</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7312520</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>133234359</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79374</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Skuorrejaureberget, Skuorrejaureberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>697327</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7312439</v>
+      </c>
+      <c r="S89" t="n">
+        <v>7</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31153-2025 artfynd.xlsx
+++ b/artfynd/A 31153-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387774</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671928</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017340</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379715</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387775</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671970</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387771</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671960</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671961</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675520</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429377</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126801482</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387772</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387773</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387767</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387768</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2357,6 +2442,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387769</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2454,6 +2544,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429379</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2551,6 +2646,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387776</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2649,6 +2749,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671973</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2746,6 +2851,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126801479</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2843,6 +2953,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429381</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2940,6 +3055,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429382</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3037,6 +3157,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671962</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3134,6 +3259,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671963</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3231,6 +3361,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671964</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3328,6 +3463,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671965</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3425,6 +3565,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671968</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3522,6 +3667,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671969</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3623,6 +3773,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675593</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3720,6 +3875,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429384</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3817,6 +3977,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126801486</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3915,6 +4080,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671972</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4013,6 +4183,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387766</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4111,6 +4286,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671955</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4208,6 +4388,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671957</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4306,6 +4491,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671948</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4403,6 +4593,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429375</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4500,6 +4695,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126801480</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4597,6 +4797,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671929</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4694,6 +4899,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671930</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4791,6 +5001,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671931</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4888,6 +5103,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671932</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4985,6 +5205,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671934</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5082,6 +5307,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671935</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5179,6 +5409,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671974</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5280,6 +5515,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675495</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5377,6 +5617,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429383</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5474,6 +5719,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126801483</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5576,6 +5826,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671944</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5678,6 +5933,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671945</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5784,6 +6044,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671946</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5890,6 +6155,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671947</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5992,6 +6262,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126801484</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6098,6 +6373,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126801485</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6204,6 +6484,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671938</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6310,6 +6595,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671939</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6426,6 +6716,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127705223</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6532,6 +6827,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387761</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6638,6 +6938,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387763</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6740,6 +7045,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671941</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6845,6 +7155,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387765</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6951,6 +7266,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379706</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7057,6 +7377,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379707</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7163,6 +7488,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379710</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7269,6 +7599,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379711</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7375,6 +7710,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379712</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7481,6 +7821,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379716</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7584,6 +7929,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671958</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7691,6 +8041,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671959</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7807,6 +8162,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133233913</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7914,6 +8274,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133235530</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8012,6 +8377,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429374</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8114,6 +8484,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441134</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8212,6 +8587,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671951</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8314,6 +8694,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126440996</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8416,6 +8801,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441387</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8513,6 +8903,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671953</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8610,6 +9005,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671952</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8712,6 +9112,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441004</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8818,6 +9223,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379709</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8920,6 +9330,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441319</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9017,6 +9432,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126387770</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9115,6 +9535,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671954</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9212,6 +9637,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126429376</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9309,6 +9739,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126801481</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9406,6 +9841,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127671936</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9513,8 +9953,103 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133234359</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>